--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV_Fiets.xlsx
@@ -388,10 +388,10 @@
         <v>16164</v>
       </c>
       <c r="C2">
-        <v>23669</v>
+        <v>23670</v>
       </c>
       <c r="D2">
-        <v>47933</v>
+        <v>47936</v>
       </c>
       <c r="E2">
         <v>68662</v>
@@ -408,7 +408,7 @@
         <v>26379</v>
       </c>
       <c r="D3">
-        <v>53087</v>
+        <v>53090</v>
       </c>
       <c r="E3">
         <v>73776</v>
@@ -425,10 +425,10 @@
         <v>22636</v>
       </c>
       <c r="D4">
-        <v>49141</v>
+        <v>49143</v>
       </c>
       <c r="E4">
-        <v>69931</v>
+        <v>69942</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -442,10 +442,10 @@
         <v>22636</v>
       </c>
       <c r="D5">
-        <v>49141</v>
+        <v>49143</v>
       </c>
       <c r="E5">
-        <v>69931</v>
+        <v>69942</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -459,10 +459,10 @@
         <v>22636</v>
       </c>
       <c r="D6">
-        <v>49141</v>
+        <v>49143</v>
       </c>
       <c r="E6">
-        <v>69931</v>
+        <v>69942</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>14463</v>
       </c>
       <c r="C7">
-        <v>21233</v>
+        <v>21245</v>
       </c>
       <c r="D7">
-        <v>44786</v>
+        <v>44808</v>
       </c>
       <c r="E7">
-        <v>64582</v>
+        <v>64625</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>14463</v>
       </c>
       <c r="C8">
-        <v>21233</v>
+        <v>21245</v>
       </c>
       <c r="D8">
-        <v>44786</v>
+        <v>44808</v>
       </c>
       <c r="E8">
-        <v>64582</v>
+        <v>64625</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>12724</v>
       </c>
       <c r="C9">
-        <v>17585</v>
+        <v>17605</v>
       </c>
       <c r="D9">
-        <v>37332</v>
+        <v>37387</v>
       </c>
       <c r="E9">
-        <v>56303</v>
+        <v>56425</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>14463</v>
       </c>
       <c r="C10">
-        <v>21233</v>
+        <v>21245</v>
       </c>
       <c r="D10">
-        <v>44786</v>
+        <v>44808</v>
       </c>
       <c r="E10">
-        <v>64582</v>
+        <v>64625</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>14463</v>
       </c>
       <c r="C11">
-        <v>21233</v>
+        <v>21245</v>
       </c>
       <c r="D11">
-        <v>44786</v>
+        <v>44808</v>
       </c>
       <c r="E11">
-        <v>64582</v>
+        <v>64625</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,10 +558,10 @@
         <v>13484</v>
       </c>
       <c r="C12">
-        <v>21592</v>
+        <v>21593</v>
       </c>
       <c r="D12">
-        <v>47248</v>
+        <v>47250</v>
       </c>
       <c r="E12">
         <v>68837</v>
@@ -578,7 +578,7 @@
         <v>26379</v>
       </c>
       <c r="D13">
-        <v>53087</v>
+        <v>53090</v>
       </c>
       <c r="E13">
         <v>73776</v>
@@ -592,10 +592,10 @@
         <v>13484</v>
       </c>
       <c r="C14">
-        <v>21592</v>
+        <v>21593</v>
       </c>
       <c r="D14">
-        <v>47248</v>
+        <v>47250</v>
       </c>
       <c r="E14">
         <v>68837</v>
@@ -609,13 +609,13 @@
         <v>14463</v>
       </c>
       <c r="C15">
-        <v>21233</v>
+        <v>21245</v>
       </c>
       <c r="D15">
-        <v>44786</v>
+        <v>44808</v>
       </c>
       <c r="E15">
-        <v>64582</v>
+        <v>64625</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -626,13 +626,13 @@
         <v>14193</v>
       </c>
       <c r="C16">
-        <v>19471</v>
+        <v>19475</v>
       </c>
       <c r="D16">
-        <v>40343</v>
+        <v>40368</v>
       </c>
       <c r="E16">
-        <v>59172</v>
+        <v>59202</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,10 +643,10 @@
         <v>13484</v>
       </c>
       <c r="C17">
-        <v>21592</v>
+        <v>21593</v>
       </c>
       <c r="D17">
-        <v>47248</v>
+        <v>47250</v>
       </c>
       <c r="E17">
         <v>68837</v>
@@ -663,7 +663,7 @@
         <v>26379</v>
       </c>
       <c r="D18">
-        <v>53087</v>
+        <v>53090</v>
       </c>
       <c r="E18">
         <v>73776</v>
@@ -677,13 +677,13 @@
         <v>14193</v>
       </c>
       <c r="C19">
-        <v>19471</v>
+        <v>19475</v>
       </c>
       <c r="D19">
-        <v>40343</v>
+        <v>40368</v>
       </c>
       <c r="E19">
-        <v>59172</v>
+        <v>59202</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -694,13 +694,13 @@
         <v>14193</v>
       </c>
       <c r="C20">
-        <v>19471</v>
+        <v>19475</v>
       </c>
       <c r="D20">
-        <v>40343</v>
+        <v>40368</v>
       </c>
       <c r="E20">
-        <v>59172</v>
+        <v>59202</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -711,13 +711,13 @@
         <v>14193</v>
       </c>
       <c r="C21">
-        <v>19471</v>
+        <v>19475</v>
       </c>
       <c r="D21">
-        <v>40343</v>
+        <v>40368</v>
       </c>
       <c r="E21">
-        <v>59172</v>
+        <v>59202</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -728,13 +728,13 @@
         <v>21902</v>
       </c>
       <c r="C22">
-        <v>34429</v>
+        <v>34435</v>
       </c>
       <c r="D22">
-        <v>62023</v>
+        <v>62032</v>
       </c>
       <c r="E22">
-        <v>79278</v>
+        <v>79297</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -745,10 +745,10 @@
         <v>16164</v>
       </c>
       <c r="C23">
-        <v>23669</v>
+        <v>23670</v>
       </c>
       <c r="D23">
-        <v>47933</v>
+        <v>47936</v>
       </c>
       <c r="E23">
         <v>68662</v>
@@ -765,10 +765,10 @@
         <v>17335</v>
       </c>
       <c r="D24">
-        <v>39315</v>
+        <v>39316</v>
       </c>
       <c r="E24">
-        <v>59395</v>
+        <v>59401</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -782,10 +782,10 @@
         <v>17335</v>
       </c>
       <c r="D25">
-        <v>39315</v>
+        <v>39316</v>
       </c>
       <c r="E25">
-        <v>59395</v>
+        <v>59401</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -799,10 +799,10 @@
         <v>17335</v>
       </c>
       <c r="D26">
-        <v>39315</v>
+        <v>39316</v>
       </c>
       <c r="E26">
-        <v>59395</v>
+        <v>59401</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -816,10 +816,10 @@
         <v>24677</v>
       </c>
       <c r="D27">
-        <v>50896</v>
+        <v>50900</v>
       </c>
       <c r="E27">
-        <v>71075</v>
+        <v>71085</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -833,10 +833,10 @@
         <v>24677</v>
       </c>
       <c r="D28">
-        <v>50896</v>
+        <v>50900</v>
       </c>
       <c r="E28">
-        <v>71075</v>
+        <v>71085</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -850,10 +850,10 @@
         <v>24677</v>
       </c>
       <c r="D29">
-        <v>50896</v>
+        <v>50900</v>
       </c>
       <c r="E29">
-        <v>71075</v>
+        <v>71085</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>29583</v>
       </c>
       <c r="C30">
-        <v>37738</v>
+        <v>37772</v>
       </c>
       <c r="D30">
-        <v>55264</v>
+        <v>55422</v>
       </c>
       <c r="E30">
-        <v>69463</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>29583</v>
       </c>
       <c r="C31">
-        <v>37738</v>
+        <v>37772</v>
       </c>
       <c r="D31">
-        <v>55264</v>
+        <v>55422</v>
       </c>
       <c r="E31">
-        <v>69463</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>32563</v>
       </c>
       <c r="C32">
-        <v>42203</v>
+        <v>42225</v>
       </c>
       <c r="D32">
-        <v>61204</v>
+        <v>61279</v>
       </c>
       <c r="E32">
-        <v>75111</v>
+        <v>75161</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>29583</v>
       </c>
       <c r="C33">
-        <v>37738</v>
+        <v>37772</v>
       </c>
       <c r="D33">
-        <v>55264</v>
+        <v>55422</v>
       </c>
       <c r="E33">
-        <v>69463</v>
+        <v>69609</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>41012</v>
+        <v>41022</v>
       </c>
       <c r="C34">
-        <v>51723</v>
+        <v>51738</v>
       </c>
       <c r="D34">
-        <v>70873</v>
+        <v>70885</v>
       </c>
       <c r="E34">
-        <v>83773</v>
+        <v>83784</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,10 +949,10 @@
         <v>40379</v>
       </c>
       <c r="C35">
-        <v>51057</v>
+        <v>51063</v>
       </c>
       <c r="D35">
-        <v>69608</v>
+        <v>69622</v>
       </c>
       <c r="E35">
         <v>83262</v>
@@ -966,13 +966,13 @@
         <v>27552</v>
       </c>
       <c r="C36">
-        <v>36973</v>
+        <v>36976</v>
       </c>
       <c r="D36">
-        <v>57419</v>
+        <v>57453</v>
       </c>
       <c r="E36">
-        <v>72417</v>
+        <v>72460</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>30313</v>
       </c>
       <c r="C37">
-        <v>37962</v>
+        <v>37971</v>
       </c>
       <c r="D37">
-        <v>54824</v>
+        <v>54937</v>
       </c>
       <c r="E37">
-        <v>68742</v>
+        <v>68874</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>30313</v>
       </c>
       <c r="C38">
-        <v>37962</v>
+        <v>37971</v>
       </c>
       <c r="D38">
-        <v>54824</v>
+        <v>54937</v>
       </c>
       <c r="E38">
-        <v>68742</v>
+        <v>68874</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>36595</v>
+        <v>36613</v>
       </c>
       <c r="C39">
-        <v>45587</v>
+        <v>45654</v>
       </c>
       <c r="D39">
-        <v>63798</v>
+        <v>63864</v>
       </c>
       <c r="E39">
-        <v>77300</v>
+        <v>77341</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>41723</v>
       </c>
       <c r="C40">
-        <v>52400</v>
+        <v>52405</v>
       </c>
       <c r="D40">
-        <v>71455</v>
+        <v>71468</v>
       </c>
       <c r="E40">
-        <v>84061</v>
+        <v>84071</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,10 +1051,10 @@
         <v>40379</v>
       </c>
       <c r="C41">
-        <v>51057</v>
+        <v>51063</v>
       </c>
       <c r="D41">
-        <v>69608</v>
+        <v>69622</v>
       </c>
       <c r="E41">
         <v>83262</v>
@@ -1068,13 +1068,13 @@
         <v>30245</v>
       </c>
       <c r="C42">
-        <v>39354</v>
+        <v>39357</v>
       </c>
       <c r="D42">
-        <v>58473</v>
+        <v>58517</v>
       </c>
       <c r="E42">
-        <v>72624</v>
+        <v>72672</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,10 +1085,10 @@
         <v>33759</v>
       </c>
       <c r="C43">
-        <v>44898</v>
+        <v>44899</v>
       </c>
       <c r="D43">
-        <v>64511</v>
+        <v>64522</v>
       </c>
       <c r="E43">
         <v>79188</v>
@@ -1102,13 +1102,13 @@
         <v>33316</v>
       </c>
       <c r="C44">
-        <v>45629</v>
+        <v>45634</v>
       </c>
       <c r="D44">
-        <v>66673</v>
+        <v>66690</v>
       </c>
       <c r="E44">
-        <v>80566</v>
+        <v>80585</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>27176</v>
       </c>
       <c r="C45">
-        <v>35893</v>
+        <v>35894</v>
       </c>
       <c r="D45">
-        <v>55658</v>
+        <v>55696</v>
       </c>
       <c r="E45">
-        <v>70496</v>
+        <v>70536</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>33007</v>
       </c>
       <c r="C46">
-        <v>42105</v>
+        <v>42111</v>
       </c>
       <c r="D46">
-        <v>60667</v>
+        <v>60723</v>
       </c>
       <c r="E46">
-        <v>74445</v>
+        <v>74490</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>31700</v>
       </c>
       <c r="C47">
-        <v>43843</v>
+        <v>43845</v>
       </c>
       <c r="D47">
-        <v>65384</v>
+        <v>65392</v>
       </c>
       <c r="E47">
-        <v>79857</v>
+        <v>79870</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1173,7 +1173,7 @@
         <v>41450</v>
       </c>
       <c r="D48">
-        <v>62052</v>
+        <v>62058</v>
       </c>
       <c r="E48">
         <v>77422</v>
@@ -1187,13 +1187,13 @@
         <v>15426</v>
       </c>
       <c r="C49">
-        <v>20198</v>
+        <v>20215</v>
       </c>
       <c r="D49">
-        <v>38321</v>
+        <v>38345</v>
       </c>
       <c r="E49">
-        <v>54758</v>
+        <v>54778</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1207,7 +1207,7 @@
         <v>21897</v>
       </c>
       <c r="D50">
-        <v>42043</v>
+        <v>42045</v>
       </c>
       <c r="E50">
         <v>61660</v>
@@ -1221,10 +1221,10 @@
         <v>13935</v>
       </c>
       <c r="C51">
-        <v>19603</v>
+        <v>19604</v>
       </c>
       <c r="D51">
-        <v>38869</v>
+        <v>38872</v>
       </c>
       <c r="E51">
         <v>57167</v>
@@ -1238,10 +1238,10 @@
         <v>14722</v>
       </c>
       <c r="C52">
-        <v>20973</v>
+        <v>20978</v>
       </c>
       <c r="D52">
-        <v>41655</v>
+        <v>41659</v>
       </c>
       <c r="E52">
         <v>60590</v>
@@ -1255,13 +1255,13 @@
         <v>13020</v>
       </c>
       <c r="C53">
-        <v>17344</v>
+        <v>17345</v>
       </c>
       <c r="D53">
-        <v>34209</v>
+        <v>34228</v>
       </c>
       <c r="E53">
-        <v>49962</v>
+        <v>49978</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>12202</v>
       </c>
       <c r="C54">
-        <v>16483</v>
+        <v>16488</v>
       </c>
       <c r="D54">
-        <v>33037</v>
+        <v>33058</v>
       </c>
       <c r="E54">
-        <v>48344</v>
+        <v>48361</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1292,7 +1292,7 @@
         <v>21897</v>
       </c>
       <c r="D55">
-        <v>42043</v>
+        <v>42045</v>
       </c>
       <c r="E55">
         <v>61660</v>
@@ -1306,10 +1306,10 @@
         <v>18866</v>
       </c>
       <c r="C56">
-        <v>26180</v>
+        <v>26188</v>
       </c>
       <c r="D56">
-        <v>48778</v>
+        <v>48782</v>
       </c>
       <c r="E56">
         <v>67736</v>
@@ -1326,10 +1326,10 @@
         <v>19931</v>
       </c>
       <c r="D57">
-        <v>40759</v>
+        <v>40762</v>
       </c>
       <c r="E57">
-        <v>60053</v>
+        <v>60058</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1343,10 +1343,10 @@
         <v>23960</v>
       </c>
       <c r="D58">
-        <v>48048</v>
+        <v>48050</v>
       </c>
       <c r="E58">
-        <v>68381</v>
+        <v>68388</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1360,10 +1360,10 @@
         <v>23960</v>
       </c>
       <c r="D59">
-        <v>48048</v>
+        <v>48050</v>
       </c>
       <c r="E59">
-        <v>68381</v>
+        <v>68388</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1377,10 +1377,10 @@
         <v>15959</v>
       </c>
       <c r="D60">
-        <v>36956</v>
+        <v>36957</v>
       </c>
       <c r="E60">
-        <v>56673</v>
+        <v>56678</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1394,10 +1394,10 @@
         <v>15959</v>
       </c>
       <c r="D61">
-        <v>36956</v>
+        <v>36957</v>
       </c>
       <c r="E61">
-        <v>56673</v>
+        <v>56678</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1411,10 +1411,10 @@
         <v>10992</v>
       </c>
       <c r="D62">
-        <v>32185</v>
+        <v>32186</v>
       </c>
       <c r="E62">
-        <v>52949</v>
+        <v>52952</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1428,10 +1428,10 @@
         <v>10992</v>
       </c>
       <c r="D63">
-        <v>32185</v>
+        <v>32186</v>
       </c>
       <c r="E63">
-        <v>52949</v>
+        <v>52952</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1445,10 +1445,10 @@
         <v>9580</v>
       </c>
       <c r="D64">
-        <v>30233</v>
+        <v>30234</v>
       </c>
       <c r="E64">
-        <v>50522</v>
+        <v>50525</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1462,10 +1462,10 @@
         <v>9580</v>
       </c>
       <c r="D65">
-        <v>30233</v>
+        <v>30234</v>
       </c>
       <c r="E65">
-        <v>50522</v>
+        <v>50525</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>19347</v>
       </c>
       <c r="C66">
-        <v>30321</v>
+        <v>30332</v>
       </c>
       <c r="D66">
-        <v>53948</v>
+        <v>53996</v>
       </c>
       <c r="E66">
-        <v>70195</v>
+        <v>70252</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,10 +1493,10 @@
         <v>23462</v>
       </c>
       <c r="C67">
-        <v>37395</v>
+        <v>37397</v>
       </c>
       <c r="D67">
-        <v>61467</v>
+        <v>61474</v>
       </c>
       <c r="E67">
         <v>77617</v>
@@ -1510,13 +1510,13 @@
         <v>19347</v>
       </c>
       <c r="C68">
-        <v>30321</v>
+        <v>30332</v>
       </c>
       <c r="D68">
-        <v>53948</v>
+        <v>53996</v>
       </c>
       <c r="E68">
-        <v>70195</v>
+        <v>70252</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,10 +1527,10 @@
         <v>23462</v>
       </c>
       <c r="C69">
-        <v>37395</v>
+        <v>37397</v>
       </c>
       <c r="D69">
-        <v>61467</v>
+        <v>61474</v>
       </c>
       <c r="E69">
         <v>77617</v>
@@ -1544,10 +1544,10 @@
         <v>23462</v>
       </c>
       <c r="C70">
-        <v>37395</v>
+        <v>37397</v>
       </c>
       <c r="D70">
-        <v>61467</v>
+        <v>61474</v>
       </c>
       <c r="E70">
         <v>77617</v>
@@ -1561,13 +1561,13 @@
         <v>27329</v>
       </c>
       <c r="C71">
-        <v>42182</v>
+        <v>42183</v>
       </c>
       <c r="D71">
-        <v>66185</v>
+        <v>66194</v>
       </c>
       <c r="E71">
-        <v>80604</v>
+        <v>80620</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>24707</v>
       </c>
       <c r="C72">
-        <v>39021</v>
+        <v>39022</v>
       </c>
       <c r="D72">
-        <v>63484</v>
+        <v>63491</v>
       </c>
       <c r="E72">
-        <v>78518</v>
+        <v>78535</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>24707</v>
       </c>
       <c r="C73">
-        <v>39021</v>
+        <v>39022</v>
       </c>
       <c r="D73">
-        <v>63484</v>
+        <v>63491</v>
       </c>
       <c r="E73">
-        <v>78518</v>
+        <v>78535</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>24707</v>
       </c>
       <c r="C74">
-        <v>39021</v>
+        <v>39022</v>
       </c>
       <c r="D74">
-        <v>63484</v>
+        <v>63491</v>
       </c>
       <c r="E74">
-        <v>78518</v>
+        <v>78535</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1632,10 +1632,10 @@
         <v>28157</v>
       </c>
       <c r="D75">
-        <v>53658</v>
+        <v>53659</v>
       </c>
       <c r="E75">
-        <v>70756</v>
+        <v>70767</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,10 +1646,10 @@
         <v>23462</v>
       </c>
       <c r="C76">
-        <v>37395</v>
+        <v>37397</v>
       </c>
       <c r="D76">
-        <v>61467</v>
+        <v>61474</v>
       </c>
       <c r="E76">
         <v>77617</v>
@@ -1666,10 +1666,10 @@
         <v>36731</v>
       </c>
       <c r="D77">
-        <v>61854</v>
+        <v>61860</v>
       </c>
       <c r="E77">
-        <v>77428</v>
+        <v>77447</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1683,10 +1683,10 @@
         <v>36731</v>
       </c>
       <c r="D78">
-        <v>61854</v>
+        <v>61860</v>
       </c>
       <c r="E78">
-        <v>77428</v>
+        <v>77447</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1700,10 +1700,10 @@
         <v>36731</v>
       </c>
       <c r="D79">
-        <v>61854</v>
+        <v>61860</v>
       </c>
       <c r="E79">
-        <v>77428</v>
+        <v>77447</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1717,10 +1717,10 @@
         <v>36731</v>
       </c>
       <c r="D80">
-        <v>61854</v>
+        <v>61860</v>
       </c>
       <c r="E80">
-        <v>77428</v>
+        <v>77447</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1734,10 +1734,10 @@
         <v>45528</v>
       </c>
       <c r="D81">
-        <v>66557</v>
+        <v>66563</v>
       </c>
       <c r="E81">
-        <v>80116</v>
+        <v>80130</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1751,10 +1751,10 @@
         <v>45528</v>
       </c>
       <c r="D82">
-        <v>66557</v>
+        <v>66563</v>
       </c>
       <c r="E82">
-        <v>80116</v>
+        <v>80130</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1768,10 +1768,10 @@
         <v>35293</v>
       </c>
       <c r="D83">
-        <v>58341</v>
+        <v>58346</v>
       </c>
       <c r="E83">
-        <v>72890</v>
+        <v>72908</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1785,10 +1785,10 @@
         <v>35293</v>
       </c>
       <c r="D84">
-        <v>58341</v>
+        <v>58346</v>
       </c>
       <c r="E84">
-        <v>72890</v>
+        <v>72908</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1802,10 +1802,10 @@
         <v>48627</v>
       </c>
       <c r="D85">
-        <v>68080</v>
+        <v>68095</v>
       </c>
       <c r="E85">
-        <v>80248</v>
+        <v>80266</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1819,10 +1819,10 @@
         <v>48627</v>
       </c>
       <c r="D86">
-        <v>68080</v>
+        <v>68095</v>
       </c>
       <c r="E86">
-        <v>80248</v>
+        <v>80266</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>34818</v>
       </c>
       <c r="C87">
-        <v>48333</v>
+        <v>48341</v>
       </c>
       <c r="D87">
-        <v>68845</v>
+        <v>68863</v>
       </c>
       <c r="E87">
-        <v>81206</v>
+        <v>81225</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>34818</v>
       </c>
       <c r="C88">
-        <v>48333</v>
+        <v>48341</v>
       </c>
       <c r="D88">
-        <v>68845</v>
+        <v>68863</v>
       </c>
       <c r="E88">
-        <v>81206</v>
+        <v>81225</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>34818</v>
       </c>
       <c r="C89">
-        <v>48333</v>
+        <v>48341</v>
       </c>
       <c r="D89">
-        <v>68845</v>
+        <v>68863</v>
       </c>
       <c r="E89">
-        <v>81206</v>
+        <v>81225</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>50891</v>
+        <v>50892</v>
       </c>
       <c r="C90">
-        <v>57465</v>
+        <v>57535</v>
       </c>
       <c r="D90">
-        <v>69668</v>
+        <v>70071</v>
       </c>
       <c r="E90">
-        <v>78349</v>
+        <v>79141</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>50886</v>
+        <v>50887</v>
       </c>
       <c r="C91">
-        <v>57408</v>
+        <v>57479</v>
       </c>
       <c r="D91">
-        <v>69514</v>
+        <v>69943</v>
       </c>
       <c r="E91">
-        <v>77995</v>
+        <v>78869</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>50863</v>
+        <v>50864</v>
       </c>
       <c r="C92">
-        <v>57161</v>
+        <v>57243</v>
       </c>
       <c r="D92">
-        <v>68857</v>
+        <v>69395</v>
       </c>
       <c r="E92">
-        <v>76479</v>
+        <v>77708</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>50932</v>
+        <v>50933</v>
       </c>
       <c r="C93">
-        <v>57912</v>
+        <v>57962</v>
       </c>
       <c r="D93">
-        <v>70857</v>
+        <v>71063</v>
       </c>
       <c r="E93">
-        <v>81091</v>
+        <v>81242</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1952,13 +1952,13 @@
         <v>49021</v>
       </c>
       <c r="C94">
-        <v>55242</v>
+        <v>55260</v>
       </c>
       <c r="D94">
-        <v>62831</v>
+        <v>63618</v>
       </c>
       <c r="E94">
-        <v>70711</v>
+        <v>72732</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1969,13 +1969,13 @@
         <v>50929</v>
       </c>
       <c r="C95">
-        <v>57872</v>
+        <v>57923</v>
       </c>
       <c r="D95">
-        <v>70749</v>
+        <v>70973</v>
       </c>
       <c r="E95">
-        <v>80841</v>
+        <v>81050</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>50871</v>
+        <v>50872</v>
       </c>
       <c r="C96">
-        <v>57244</v>
+        <v>57323</v>
       </c>
       <c r="D96">
-        <v>69080</v>
+        <v>69581</v>
       </c>
       <c r="E96">
-        <v>76993</v>
+        <v>78102</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>50932</v>
+        <v>50933</v>
       </c>
       <c r="C97">
-        <v>57912</v>
+        <v>57962</v>
       </c>
       <c r="D97">
-        <v>70857</v>
+        <v>71063</v>
       </c>
       <c r="E97">
-        <v>81091</v>
+        <v>81242</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2017,16 +2017,16 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>47266</v>
+        <v>47268</v>
       </c>
       <c r="C98">
-        <v>54602</v>
+        <v>54657</v>
       </c>
       <c r="D98">
-        <v>68551</v>
+        <v>68888</v>
       </c>
       <c r="E98">
-        <v>79910</v>
+        <v>80174</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2034,16 +2034,16 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>47218</v>
+        <v>47220</v>
       </c>
       <c r="C99">
-        <v>54306</v>
+        <v>54370</v>
       </c>
       <c r="D99">
-        <v>67741</v>
+        <v>68210</v>
       </c>
       <c r="E99">
-        <v>78339</v>
+        <v>79031</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2054,13 +2054,13 @@
         <v>48201</v>
       </c>
       <c r="C100">
-        <v>54706</v>
+        <v>54769</v>
       </c>
       <c r="D100">
-        <v>67547</v>
+        <v>67829</v>
       </c>
       <c r="E100">
-        <v>77957</v>
+        <v>78338</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2071,13 +2071,13 @@
         <v>48187</v>
       </c>
       <c r="C101">
-        <v>54559</v>
+        <v>54628</v>
       </c>
       <c r="D101">
-        <v>67106</v>
+        <v>67451</v>
       </c>
       <c r="E101">
-        <v>77009</v>
+        <v>77609</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2088,13 +2088,13 @@
         <v>48213</v>
       </c>
       <c r="C102">
-        <v>54843</v>
+        <v>54900</v>
       </c>
       <c r="D102">
-        <v>67956</v>
+        <v>68180</v>
       </c>
       <c r="E102">
-        <v>78838</v>
+        <v>79016</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2105,13 +2105,13 @@
         <v>43874</v>
       </c>
       <c r="C103">
-        <v>51436</v>
+        <v>51549</v>
       </c>
       <c r="D103">
-        <v>66251</v>
+        <v>66744</v>
       </c>
       <c r="E103">
-        <v>78595</v>
+        <v>78929</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2122,13 +2122,13 @@
         <v>43874</v>
       </c>
       <c r="C104">
-        <v>51436</v>
+        <v>51549</v>
       </c>
       <c r="D104">
-        <v>66251</v>
+        <v>66744</v>
       </c>
       <c r="E104">
-        <v>78595</v>
+        <v>78929</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>45158</v>
       </c>
       <c r="C105">
-        <v>54832</v>
+        <v>54854</v>
       </c>
       <c r="D105">
-        <v>71174</v>
+        <v>71291</v>
       </c>
       <c r="E105">
-        <v>82784</v>
+        <v>82905</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2156,13 +2156,13 @@
         <v>48342</v>
       </c>
       <c r="C106">
-        <v>59833</v>
+        <v>59883</v>
       </c>
       <c r="D106">
-        <v>76869</v>
+        <v>76939</v>
       </c>
       <c r="E106">
-        <v>87110</v>
+        <v>87150</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2173,13 +2173,13 @@
         <v>48342</v>
       </c>
       <c r="C107">
-        <v>59833</v>
+        <v>59883</v>
       </c>
       <c r="D107">
-        <v>76869</v>
+        <v>76939</v>
       </c>
       <c r="E107">
-        <v>87110</v>
+        <v>87150</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,10 +2190,10 @@
         <v>52387</v>
       </c>
       <c r="C108">
-        <v>65016</v>
+        <v>65017</v>
       </c>
       <c r="D108">
-        <v>80911</v>
+        <v>80918</v>
       </c>
       <c r="E108">
         <v>90858</v>
@@ -2204,16 +2204,16 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>43301</v>
+        <v>43304</v>
       </c>
       <c r="C109">
-        <v>53257</v>
+        <v>53379</v>
       </c>
       <c r="D109">
-        <v>69806</v>
+        <v>69976</v>
       </c>
       <c r="E109">
-        <v>81649</v>
+        <v>81780</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2221,16 +2221,16 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>43301</v>
+        <v>43304</v>
       </c>
       <c r="C110">
-        <v>53257</v>
+        <v>53379</v>
       </c>
       <c r="D110">
-        <v>69806</v>
+        <v>69976</v>
       </c>
       <c r="E110">
-        <v>81649</v>
+        <v>81780</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2238,16 +2238,16 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>43066</v>
+        <v>43068</v>
       </c>
       <c r="C111">
-        <v>52644</v>
+        <v>52792</v>
       </c>
       <c r="D111">
-        <v>68416</v>
+        <v>68713</v>
       </c>
       <c r="E111">
-        <v>79985</v>
+        <v>80431</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>43702</v>
+        <v>43711</v>
       </c>
       <c r="C112">
-        <v>51598</v>
+        <v>51847</v>
       </c>
       <c r="D112">
-        <v>66547</v>
+        <v>67170</v>
       </c>
       <c r="E112">
-        <v>78958</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>41720</v>
       </c>
       <c r="C113">
-        <v>51735</v>
+        <v>51834</v>
       </c>
       <c r="D113">
-        <v>68707</v>
+        <v>68888</v>
       </c>
       <c r="E113">
-        <v>80838</v>
+        <v>80995</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>45460</v>
       </c>
       <c r="C114">
-        <v>56786</v>
+        <v>56841</v>
       </c>
       <c r="D114">
-        <v>74461</v>
+        <v>74531</v>
       </c>
       <c r="E114">
-        <v>85352</v>
+        <v>85393</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>43673</v>
+        <v>43683</v>
       </c>
       <c r="C115">
-        <v>51480</v>
+        <v>51739</v>
       </c>
       <c r="D115">
-        <v>66261</v>
+        <v>66944</v>
       </c>
       <c r="E115">
-        <v>78474</v>
+        <v>78964</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>43702</v>
+        <v>43711</v>
       </c>
       <c r="C116">
-        <v>51598</v>
+        <v>51847</v>
       </c>
       <c r="D116">
-        <v>66547</v>
+        <v>67170</v>
       </c>
       <c r="E116">
-        <v>78958</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>41733</v>
       </c>
       <c r="C117">
-        <v>51771</v>
+        <v>51869</v>
       </c>
       <c r="D117">
-        <v>68791</v>
+        <v>68964</v>
       </c>
       <c r="E117">
-        <v>80939</v>
+        <v>81077</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>51365</v>
       </c>
       <c r="C118">
-        <v>64389</v>
+        <v>64397</v>
       </c>
       <c r="D118">
-        <v>81410</v>
+        <v>81418</v>
       </c>
       <c r="E118">
-        <v>90528</v>
+        <v>90534</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,10 +2377,10 @@
         <v>47008</v>
       </c>
       <c r="C119">
-        <v>59526</v>
+        <v>59532</v>
       </c>
       <c r="D119">
-        <v>76802</v>
+        <v>76809</v>
       </c>
       <c r="E119">
         <v>88019</v>
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>48691</v>
+        <v>48692</v>
       </c>
       <c r="C120">
-        <v>55916</v>
+        <v>55961</v>
       </c>
       <c r="D120">
-        <v>69413</v>
+        <v>69688</v>
       </c>
       <c r="E120">
-        <v>80201</v>
+        <v>80404</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>48691</v>
+        <v>48692</v>
       </c>
       <c r="C121">
-        <v>55916</v>
+        <v>55961</v>
       </c>
       <c r="D121">
-        <v>69413</v>
+        <v>69688</v>
       </c>
       <c r="E121">
-        <v>80201</v>
+        <v>80404</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>45228</v>
       </c>
       <c r="C122">
-        <v>54778</v>
+        <v>54823</v>
       </c>
       <c r="D122">
-        <v>70492</v>
+        <v>70674</v>
       </c>
       <c r="E122">
-        <v>81903</v>
+        <v>82027</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>45143</v>
       </c>
       <c r="C123">
-        <v>54565</v>
+        <v>54614</v>
       </c>
       <c r="D123">
-        <v>70008</v>
+        <v>70241</v>
       </c>
       <c r="E123">
-        <v>81326</v>
+        <v>81560</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>45228</v>
       </c>
       <c r="C124">
-        <v>54778</v>
+        <v>54823</v>
       </c>
       <c r="D124">
-        <v>70492</v>
+        <v>70674</v>
       </c>
       <c r="E124">
-        <v>81903</v>
+        <v>82027</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2479,13 +2479,13 @@
         <v>44457</v>
       </c>
       <c r="C125">
-        <v>53950</v>
+        <v>54010</v>
       </c>
       <c r="D125">
-        <v>69721</v>
+        <v>69900</v>
       </c>
       <c r="E125">
-        <v>81142</v>
+        <v>81270</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2496,13 +2496,13 @@
         <v>48131</v>
       </c>
       <c r="C126">
-        <v>58669</v>
+        <v>58706</v>
       </c>
       <c r="D126">
-        <v>74995</v>
+        <v>75066</v>
       </c>
       <c r="E126">
-        <v>85384</v>
+        <v>85422</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>50552</v>
+        <v>50555</v>
       </c>
       <c r="C127">
-        <v>61023</v>
+        <v>61092</v>
       </c>
       <c r="D127">
-        <v>76779</v>
+        <v>76863</v>
       </c>
       <c r="E127">
-        <v>86751</v>
+        <v>86795</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,10 +2530,10 @@
         <v>53988</v>
       </c>
       <c r="C128">
-        <v>64862</v>
+        <v>64869</v>
       </c>
       <c r="D128">
-        <v>79479</v>
+        <v>79488</v>
       </c>
       <c r="E128">
         <v>89655</v>
@@ -2547,10 +2547,10 @@
         <v>53988</v>
       </c>
       <c r="C129">
-        <v>64862</v>
+        <v>64869</v>
       </c>
       <c r="D129">
-        <v>79479</v>
+        <v>79488</v>
       </c>
       <c r="E129">
         <v>89655</v>
@@ -2561,16 +2561,16 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>50768</v>
+        <v>50769</v>
       </c>
       <c r="C130">
-        <v>57128</v>
+        <v>57170</v>
       </c>
       <c r="D130">
-        <v>69538</v>
+        <v>69788</v>
       </c>
       <c r="E130">
-        <v>79732</v>
+        <v>79971</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2578,16 +2578,16 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>50758</v>
+        <v>50760</v>
       </c>
       <c r="C131">
-        <v>56622</v>
+        <v>56683</v>
       </c>
       <c r="D131">
-        <v>67958</v>
+        <v>68473</v>
       </c>
       <c r="E131">
-        <v>76149</v>
+        <v>77232</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2595,16 +2595,16 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>50759</v>
+        <v>50761</v>
       </c>
       <c r="C132">
-        <v>56660</v>
+        <v>56719</v>
       </c>
       <c r="D132">
-        <v>68076</v>
+        <v>68571</v>
       </c>
       <c r="E132">
-        <v>76416</v>
+        <v>77436</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2612,16 +2612,16 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>50763</v>
+        <v>50764</v>
       </c>
       <c r="C133">
-        <v>56840</v>
+        <v>56892</v>
       </c>
       <c r="D133">
-        <v>68637</v>
+        <v>69038</v>
       </c>
       <c r="E133">
-        <v>77689</v>
+        <v>78409</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2632,13 +2632,13 @@
         <v>51118</v>
       </c>
       <c r="C134">
-        <v>57318</v>
+        <v>57329</v>
       </c>
       <c r="D134">
-        <v>68881</v>
+        <v>69358</v>
       </c>
       <c r="E134">
-        <v>76928</v>
+        <v>77928</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2649,13 +2649,13 @@
         <v>49741</v>
       </c>
       <c r="C135">
-        <v>55876</v>
+        <v>55921</v>
       </c>
       <c r="D135">
-        <v>68306</v>
+        <v>68596</v>
       </c>
       <c r="E135">
-        <v>78764</v>
+        <v>79068</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2666,13 +2666,13 @@
         <v>48153</v>
       </c>
       <c r="C136">
-        <v>54056</v>
+        <v>54115</v>
       </c>
       <c r="D136">
-        <v>66435</v>
+        <v>66844</v>
       </c>
       <c r="E136">
-        <v>77089</v>
+        <v>77558</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2683,13 +2683,13 @@
         <v>48165</v>
       </c>
       <c r="C137">
-        <v>54178</v>
+        <v>54233</v>
       </c>
       <c r="D137">
-        <v>66833</v>
+        <v>67172</v>
       </c>
       <c r="E137">
-        <v>77918</v>
+        <v>78163</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2700,13 +2700,13 @@
         <v>48165</v>
       </c>
       <c r="C138">
-        <v>54178</v>
+        <v>54233</v>
       </c>
       <c r="D138">
-        <v>66833</v>
+        <v>67172</v>
       </c>
       <c r="E138">
-        <v>77918</v>
+        <v>78163</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>48643</v>
       </c>
       <c r="C139">
-        <v>55042</v>
+        <v>55108</v>
       </c>
       <c r="D139">
-        <v>67959</v>
+        <v>68271</v>
       </c>
       <c r="E139">
-        <v>78831</v>
+        <v>79051</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2734,10 +2734,10 @@
         <v>48695</v>
       </c>
       <c r="C140">
-        <v>56190</v>
+        <v>56228</v>
       </c>
       <c r="D140">
-        <v>63233</v>
+        <v>63308</v>
       </c>
       <c r="E140">
         <v>75696</v>
@@ -2751,13 +2751,13 @@
         <v>48643</v>
       </c>
       <c r="C141">
-        <v>55042</v>
+        <v>55108</v>
       </c>
       <c r="D141">
-        <v>67959</v>
+        <v>68271</v>
       </c>
       <c r="E141">
-        <v>78831</v>
+        <v>79051</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>48639</v>
       </c>
       <c r="C142">
-        <v>54990</v>
+        <v>55059</v>
       </c>
       <c r="D142">
-        <v>67797</v>
+        <v>68137</v>
       </c>
       <c r="E142">
-        <v>78494</v>
+        <v>78803</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>46513</v>
       </c>
       <c r="C143">
-        <v>54037</v>
+        <v>54142</v>
       </c>
       <c r="D143">
-        <v>65822</v>
+        <v>66446</v>
       </c>
       <c r="E143">
-        <v>75667</v>
+        <v>76883</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>47259</v>
       </c>
       <c r="C144">
-        <v>56060</v>
+        <v>56115</v>
       </c>
       <c r="D144">
-        <v>70697</v>
+        <v>70847</v>
       </c>
       <c r="E144">
-        <v>81641</v>
+        <v>81750</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>47259</v>
       </c>
       <c r="C145">
-        <v>56060</v>
+        <v>56115</v>
       </c>
       <c r="D145">
-        <v>70697</v>
+        <v>70847</v>
       </c>
       <c r="E145">
-        <v>81641</v>
+        <v>81750</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,10 +2836,10 @@
         <v>53551</v>
       </c>
       <c r="C146">
-        <v>64006</v>
+        <v>64015</v>
       </c>
       <c r="D146">
-        <v>77427</v>
+        <v>77447</v>
       </c>
       <c r="E146">
         <v>87941</v>
@@ -2853,13 +2853,13 @@
         <v>48860</v>
       </c>
       <c r="C147">
-        <v>57407</v>
+        <v>57431</v>
       </c>
       <c r="D147">
-        <v>72806</v>
+        <v>72855</v>
       </c>
       <c r="E147">
-        <v>83645</v>
+        <v>83675</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>46372</v>
       </c>
       <c r="C148">
-        <v>53947</v>
+        <v>53982</v>
       </c>
       <c r="D148">
-        <v>68190</v>
+        <v>68308</v>
       </c>
       <c r="E148">
-        <v>79515</v>
+        <v>79613</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>45492</v>
       </c>
       <c r="C149">
-        <v>51104</v>
+        <v>51130</v>
       </c>
       <c r="D149">
-        <v>63634</v>
+        <v>63929</v>
       </c>
       <c r="E149">
-        <v>74801</v>
+        <v>75021</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>45492</v>
       </c>
       <c r="C150">
-        <v>51104</v>
+        <v>51130</v>
       </c>
       <c r="D150">
-        <v>63634</v>
+        <v>63929</v>
       </c>
       <c r="E150">
-        <v>74801</v>
+        <v>75021</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>45493</v>
       </c>
       <c r="C151">
-        <v>50951</v>
+        <v>50981</v>
       </c>
       <c r="D151">
-        <v>63050</v>
+        <v>63443</v>
       </c>
       <c r="E151">
-        <v>73522</v>
+        <v>74065</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>45492</v>
       </c>
       <c r="C152">
-        <v>51104</v>
+        <v>51130</v>
       </c>
       <c r="D152">
-        <v>63634</v>
+        <v>63929</v>
       </c>
       <c r="E152">
-        <v>74801</v>
+        <v>75021</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2955,10 +2955,10 @@
         <v>47896</v>
       </c>
       <c r="C153">
-        <v>57845</v>
+        <v>57859</v>
       </c>
       <c r="D153">
-        <v>73833</v>
+        <v>73843</v>
       </c>
       <c r="E153">
         <v>85713</v>
@@ -2972,10 +2972,10 @@
         <v>47896</v>
       </c>
       <c r="C154">
-        <v>57845</v>
+        <v>57859</v>
       </c>
       <c r="D154">
-        <v>73833</v>
+        <v>73843</v>
       </c>
       <c r="E154">
         <v>85713</v>
@@ -2989,13 +2989,13 @@
         <v>41187</v>
       </c>
       <c r="C155">
-        <v>48325</v>
+        <v>48368</v>
       </c>
       <c r="D155">
-        <v>62765</v>
+        <v>62907</v>
       </c>
       <c r="E155">
-        <v>74710</v>
+        <v>74815</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>41187</v>
       </c>
       <c r="C156">
-        <v>48325</v>
+        <v>48368</v>
       </c>
       <c r="D156">
-        <v>62765</v>
+        <v>62907</v>
       </c>
       <c r="E156">
-        <v>74710</v>
+        <v>74815</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>43670</v>
       </c>
       <c r="C157">
-        <v>51740</v>
+        <v>51771</v>
       </c>
       <c r="D157">
-        <v>67592</v>
+        <v>67653</v>
       </c>
       <c r="E157">
-        <v>79344</v>
+        <v>79376</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>43322</v>
       </c>
       <c r="C158">
-        <v>50880</v>
+        <v>50901</v>
       </c>
       <c r="D158">
-        <v>65449</v>
+        <v>65573</v>
       </c>
       <c r="E158">
-        <v>77124</v>
+        <v>77223</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>43305</v>
       </c>
       <c r="C159">
-        <v>48713</v>
+        <v>48744</v>
       </c>
       <c r="D159">
-        <v>61231</v>
+        <v>61558</v>
       </c>
       <c r="E159">
-        <v>72623</v>
+        <v>72854</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>40720</v>
       </c>
       <c r="C160">
-        <v>48228</v>
+        <v>48238</v>
       </c>
       <c r="D160">
-        <v>63077</v>
+        <v>63199</v>
       </c>
       <c r="E160">
-        <v>75157</v>
+        <v>75266</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3091,13 +3091,13 @@
         <v>42880</v>
       </c>
       <c r="C161">
-        <v>52054</v>
+        <v>52087</v>
       </c>
       <c r="D161">
-        <v>68809</v>
+        <v>68867</v>
       </c>
       <c r="E161">
-        <v>80659</v>
+        <v>80695</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,10 +3108,10 @@
         <v>46243</v>
       </c>
       <c r="C162">
-        <v>56441</v>
+        <v>56445</v>
       </c>
       <c r="D162">
-        <v>72742</v>
+        <v>72753</v>
       </c>
       <c r="E162">
         <v>84924</v>
@@ -3125,13 +3125,13 @@
         <v>44062</v>
       </c>
       <c r="C163">
-        <v>49954</v>
+        <v>49988</v>
       </c>
       <c r="D163">
-        <v>62741</v>
+        <v>63104</v>
       </c>
       <c r="E163">
-        <v>74216</v>
+        <v>74449</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>44208</v>
       </c>
       <c r="C164">
-        <v>52145</v>
+        <v>52167</v>
       </c>
       <c r="D164">
-        <v>66909</v>
+        <v>67044</v>
       </c>
       <c r="E164">
-        <v>78548</v>
+        <v>78646</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>41144</v>
       </c>
       <c r="C165">
-        <v>48917</v>
+        <v>48925</v>
       </c>
       <c r="D165">
-        <v>63900</v>
+        <v>64042</v>
       </c>
       <c r="E165">
-        <v>75873</v>
+        <v>75981</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>41144</v>
       </c>
       <c r="C166">
-        <v>48917</v>
+        <v>48925</v>
       </c>
       <c r="D166">
-        <v>63900</v>
+        <v>64042</v>
       </c>
       <c r="E166">
-        <v>75873</v>
+        <v>75981</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>43384</v>
       </c>
       <c r="C167">
-        <v>52992</v>
+        <v>53046</v>
       </c>
       <c r="D167">
-        <v>70020</v>
+        <v>70084</v>
       </c>
       <c r="E167">
-        <v>81790</v>
+        <v>81827</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3210,13 +3210,13 @@
         <v>47921</v>
       </c>
       <c r="C168">
-        <v>59271</v>
+        <v>59283</v>
       </c>
       <c r="D168">
-        <v>76496</v>
+        <v>76505</v>
       </c>
       <c r="E168">
-        <v>87362</v>
+        <v>87369</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3227,13 +3227,13 @@
         <v>49533</v>
       </c>
       <c r="C169">
-        <v>56401</v>
+        <v>56468</v>
       </c>
       <c r="D169">
-        <v>69451</v>
+        <v>69771</v>
       </c>
       <c r="E169">
-        <v>80034</v>
+        <v>80294</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>49611</v>
       </c>
       <c r="C170">
-        <v>55612</v>
+        <v>55630</v>
       </c>
       <c r="D170">
-        <v>67747</v>
+        <v>68024</v>
       </c>
       <c r="E170">
-        <v>77524</v>
+        <v>78062</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3261,13 +3261,13 @@
         <v>49540</v>
       </c>
       <c r="C171">
-        <v>56442</v>
+        <v>56508</v>
       </c>
       <c r="D171">
-        <v>69557</v>
+        <v>69858</v>
       </c>
       <c r="E171">
-        <v>80251</v>
+        <v>80454</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>49605</v>
       </c>
       <c r="C172">
-        <v>55812</v>
+        <v>55827</v>
       </c>
       <c r="D172">
-        <v>68455</v>
+        <v>68641</v>
       </c>
       <c r="E172">
-        <v>79138</v>
+        <v>79309</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>49616</v>
       </c>
       <c r="C173">
-        <v>55448</v>
+        <v>55469</v>
       </c>
       <c r="D173">
-        <v>67168</v>
+        <v>67519</v>
       </c>
       <c r="E173">
-        <v>76204</v>
+        <v>77042</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3312,13 +3312,13 @@
         <v>49954</v>
       </c>
       <c r="C174">
-        <v>55560</v>
+        <v>55567</v>
       </c>
       <c r="D174">
-        <v>66711</v>
+        <v>67100</v>
       </c>
       <c r="E174">
-        <v>74984</v>
+        <v>76054</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3329,13 +3329,13 @@
         <v>50220</v>
       </c>
       <c r="C175">
-        <v>59881</v>
+        <v>59907</v>
       </c>
       <c r="D175">
-        <v>75804</v>
+        <v>75859</v>
       </c>
       <c r="E175">
-        <v>86270</v>
+        <v>86304</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3346,13 +3346,13 @@
         <v>47281</v>
       </c>
       <c r="C176">
-        <v>55901</v>
+        <v>55940</v>
       </c>
       <c r="D176">
-        <v>71047</v>
+        <v>71181</v>
       </c>
       <c r="E176">
-        <v>82415</v>
+        <v>82526</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3363,13 +3363,13 @@
         <v>47281</v>
       </c>
       <c r="C177">
-        <v>55901</v>
+        <v>55940</v>
       </c>
       <c r="D177">
-        <v>71047</v>
+        <v>71181</v>
       </c>
       <c r="E177">
-        <v>82415</v>
+        <v>82526</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3380,13 +3380,13 @@
         <v>47535</v>
       </c>
       <c r="C178">
-        <v>53585</v>
+        <v>53614</v>
       </c>
       <c r="D178">
-        <v>66501</v>
+        <v>66852</v>
       </c>
       <c r="E178">
-        <v>77924</v>
+        <v>78198</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3397,13 +3397,13 @@
         <v>47346</v>
       </c>
       <c r="C179">
-        <v>55529</v>
+        <v>55560</v>
       </c>
       <c r="D179">
-        <v>70215</v>
+        <v>70328</v>
       </c>
       <c r="E179">
-        <v>81460</v>
+        <v>81570</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3414,13 +3414,13 @@
         <v>54212</v>
       </c>
       <c r="C180">
-        <v>65175</v>
+        <v>65178</v>
       </c>
       <c r="D180">
-        <v>80836</v>
+        <v>80843</v>
       </c>
       <c r="E180">
-        <v>90146</v>
+        <v>90151</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3431,13 +3431,13 @@
         <v>54212</v>
       </c>
       <c r="C181">
-        <v>65175</v>
+        <v>65178</v>
       </c>
       <c r="D181">
-        <v>80836</v>
+        <v>80843</v>
       </c>
       <c r="E181">
-        <v>90146</v>
+        <v>90151</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3448,13 +3448,13 @@
         <v>48672</v>
       </c>
       <c r="C182">
-        <v>58932</v>
+        <v>58937</v>
       </c>
       <c r="D182">
-        <v>75766</v>
+        <v>75777</v>
       </c>
       <c r="E182">
-        <v>86624</v>
+        <v>86630</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3468,10 +3468,10 @@
         <v>55081</v>
       </c>
       <c r="D183">
-        <v>72397</v>
+        <v>72407</v>
       </c>
       <c r="E183">
-        <v>84353</v>
+        <v>84359</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>47544</v>
       </c>
       <c r="C184">
-        <v>56986</v>
+        <v>57007</v>
       </c>
       <c r="D184">
-        <v>73363</v>
+        <v>73426</v>
       </c>
       <c r="E184">
-        <v>84370</v>
+        <v>84406</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>47544</v>
       </c>
       <c r="C185">
-        <v>56986</v>
+        <v>57007</v>
       </c>
       <c r="D185">
-        <v>73363</v>
+        <v>73426</v>
       </c>
       <c r="E185">
-        <v>84370</v>
+        <v>84406</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,10 +3516,10 @@
         <v>48116</v>
       </c>
       <c r="C186">
-        <v>58756</v>
+        <v>58759</v>
       </c>
       <c r="D186">
-        <v>75146</v>
+        <v>75156</v>
       </c>
       <c r="E186">
         <v>86755</v>
@@ -3533,13 +3533,13 @@
         <v>45091</v>
       </c>
       <c r="C187">
-        <v>54037</v>
+        <v>54054</v>
       </c>
       <c r="D187">
-        <v>70474</v>
+        <v>70534</v>
       </c>
       <c r="E187">
-        <v>81956</v>
+        <v>81991</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3550,10 +3550,10 @@
         <v>46936</v>
       </c>
       <c r="C188">
-        <v>57286</v>
+        <v>57294</v>
       </c>
       <c r="D188">
-        <v>73952</v>
+        <v>73963</v>
       </c>
       <c r="E188">
         <v>86001</v>
@@ -3567,13 +3567,13 @@
         <v>48116</v>
       </c>
       <c r="C189">
-        <v>58538</v>
+        <v>58544</v>
       </c>
       <c r="D189">
-        <v>75710</v>
+        <v>75721</v>
       </c>
       <c r="E189">
-        <v>86680</v>
+        <v>86687</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3584,13 +3584,13 @@
         <v>48116</v>
       </c>
       <c r="C190">
-        <v>58538</v>
+        <v>58544</v>
       </c>
       <c r="D190">
-        <v>75710</v>
+        <v>75721</v>
       </c>
       <c r="E190">
-        <v>86680</v>
+        <v>86687</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3598,16 +3598,16 @@
         <v>190</v>
       </c>
       <c r="B191">
-        <v>47842</v>
+        <v>47843</v>
       </c>
       <c r="C191">
-        <v>57328</v>
+        <v>57364</v>
       </c>
       <c r="D191">
-        <v>73591</v>
+        <v>73655</v>
       </c>
       <c r="E191">
-        <v>84490</v>
+        <v>84526</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>45091</v>
       </c>
       <c r="C192">
-        <v>54037</v>
+        <v>54054</v>
       </c>
       <c r="D192">
-        <v>70474</v>
+        <v>70534</v>
       </c>
       <c r="E192">
-        <v>81956</v>
+        <v>81991</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3635,13 +3635,13 @@
         <v>48213</v>
       </c>
       <c r="C193">
-        <v>54843</v>
+        <v>54900</v>
       </c>
       <c r="D193">
-        <v>67956</v>
+        <v>68180</v>
       </c>
       <c r="E193">
-        <v>78838</v>
+        <v>79016</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3652,13 +3652,13 @@
         <v>48167</v>
       </c>
       <c r="C194">
-        <v>54344</v>
+        <v>54422</v>
       </c>
       <c r="D194">
-        <v>66460</v>
+        <v>66896</v>
       </c>
       <c r="E194">
-        <v>75620</v>
+        <v>76539</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3669,13 +3669,13 @@
         <v>49523</v>
       </c>
       <c r="C195">
-        <v>56339</v>
+        <v>56408</v>
       </c>
       <c r="D195">
-        <v>69292</v>
+        <v>69639</v>
       </c>
       <c r="E195">
-        <v>79710</v>
+        <v>80054</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3686,13 +3686,13 @@
         <v>45864</v>
       </c>
       <c r="C196">
-        <v>52443</v>
+        <v>52530</v>
       </c>
       <c r="D196">
-        <v>66077</v>
+        <v>66450</v>
       </c>
       <c r="E196">
-        <v>77767</v>
+        <v>78014</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>45340</v>
       </c>
       <c r="C197">
-        <v>51995</v>
+        <v>52032</v>
       </c>
       <c r="D197">
-        <v>65735</v>
+        <v>66064</v>
       </c>
       <c r="E197">
-        <v>77478</v>
+        <v>77731</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>45304</v>
       </c>
       <c r="C198">
-        <v>51662</v>
+        <v>51706</v>
       </c>
       <c r="D198">
-        <v>64702</v>
+        <v>65190</v>
       </c>
       <c r="E198">
-        <v>75443</v>
+        <v>76237</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>45509</v>
       </c>
       <c r="C199">
-        <v>54248</v>
+        <v>54277</v>
       </c>
       <c r="D199">
-        <v>69292</v>
+        <v>69476</v>
       </c>
       <c r="E199">
-        <v>80546</v>
+        <v>80868</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>45643</v>
       </c>
       <c r="C200">
-        <v>54643</v>
+        <v>54668</v>
       </c>
       <c r="D200">
-        <v>70318</v>
+        <v>70430</v>
       </c>
       <c r="E200">
-        <v>81824</v>
+        <v>81929</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>47769</v>
       </c>
       <c r="C201">
-        <v>57826</v>
+        <v>57849</v>
       </c>
       <c r="D201">
-        <v>73319</v>
+        <v>73482</v>
       </c>
       <c r="E201">
-        <v>83335</v>
+        <v>83538</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,10 +3788,10 @@
         <v>49049</v>
       </c>
       <c r="C202">
-        <v>60176</v>
+        <v>60182</v>
       </c>
       <c r="D202">
-        <v>72947</v>
+        <v>72981</v>
       </c>
       <c r="E202">
         <v>84237</v>
@@ -3805,13 +3805,13 @@
         <v>46329</v>
       </c>
       <c r="C203">
-        <v>55154</v>
+        <v>55207</v>
       </c>
       <c r="D203">
-        <v>70564</v>
+        <v>70684</v>
       </c>
       <c r="E203">
-        <v>81979</v>
+        <v>82082</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3819,16 +3819,16 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>44029</v>
+        <v>44032</v>
       </c>
       <c r="C204">
-        <v>53315</v>
+        <v>53388</v>
       </c>
       <c r="D204">
-        <v>69539</v>
+        <v>69688</v>
       </c>
       <c r="E204">
-        <v>81348</v>
+        <v>81469</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3836,16 +3836,16 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>47294</v>
+        <v>47296</v>
       </c>
       <c r="C205">
-        <v>57792</v>
+        <v>57829</v>
       </c>
       <c r="D205">
-        <v>74688</v>
+        <v>74749</v>
       </c>
       <c r="E205">
-        <v>85439</v>
+        <v>85475</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3856,13 +3856,13 @@
         <v>28289</v>
       </c>
       <c r="C206">
-        <v>33776</v>
+        <v>33801</v>
       </c>
       <c r="D206">
-        <v>49398</v>
+        <v>49664</v>
       </c>
       <c r="E206">
-        <v>64323</v>
+        <v>64720</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3873,13 +3873,13 @@
         <v>25347</v>
       </c>
       <c r="C207">
-        <v>29892</v>
+        <v>29906</v>
       </c>
       <c r="D207">
-        <v>44763</v>
+        <v>44999</v>
       </c>
       <c r="E207">
-        <v>59854</v>
+        <v>60251</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3890,13 +3890,13 @@
         <v>25347</v>
       </c>
       <c r="C208">
-        <v>29892</v>
+        <v>29906</v>
       </c>
       <c r="D208">
-        <v>44763</v>
+        <v>44999</v>
       </c>
       <c r="E208">
-        <v>59854</v>
+        <v>60251</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3907,13 +3907,13 @@
         <v>28270</v>
       </c>
       <c r="C209">
-        <v>33281</v>
+        <v>33314</v>
       </c>
       <c r="D209">
-        <v>47157</v>
+        <v>47594</v>
       </c>
       <c r="E209">
-        <v>59947</v>
+        <v>61470</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3924,13 +3924,13 @@
         <v>25347</v>
       </c>
       <c r="C210">
-        <v>29892</v>
+        <v>29906</v>
       </c>
       <c r="D210">
-        <v>44763</v>
+        <v>44999</v>
       </c>
       <c r="E210">
-        <v>59854</v>
+        <v>60251</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3941,13 +3941,13 @@
         <v>25375</v>
       </c>
       <c r="C211">
-        <v>32497</v>
+        <v>32507</v>
       </c>
       <c r="D211">
-        <v>51726</v>
+        <v>51797</v>
       </c>
       <c r="E211">
-        <v>67183</v>
+        <v>67347</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3958,13 +3958,13 @@
         <v>28035</v>
       </c>
       <c r="C212">
-        <v>36934</v>
+        <v>36944</v>
       </c>
       <c r="D212">
-        <v>56634</v>
+        <v>56771</v>
       </c>
       <c r="E212">
-        <v>71200</v>
+        <v>71417</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3975,13 +3975,13 @@
         <v>25347</v>
       </c>
       <c r="C213">
-        <v>29892</v>
+        <v>29906</v>
       </c>
       <c r="D213">
-        <v>44763</v>
+        <v>44999</v>
       </c>
       <c r="E213">
-        <v>59854</v>
+        <v>60251</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3995,10 +3995,10 @@
         <v>28455</v>
       </c>
       <c r="D214">
-        <v>46668</v>
+        <v>46712</v>
       </c>
       <c r="E214">
-        <v>61966</v>
+        <v>62116</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4012,10 +4012,10 @@
         <v>28455</v>
       </c>
       <c r="D215">
-        <v>46668</v>
+        <v>46712</v>
       </c>
       <c r="E215">
-        <v>61966</v>
+        <v>62116</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>21461</v>
       </c>
       <c r="C216">
-        <v>26808</v>
+        <v>26810</v>
       </c>
       <c r="D216">
-        <v>44950</v>
+        <v>45012</v>
       </c>
       <c r="E216">
-        <v>60530</v>
+        <v>60690</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>22575</v>
       </c>
       <c r="C217">
-        <v>28831</v>
+        <v>28836</v>
       </c>
       <c r="D217">
-        <v>47612</v>
+        <v>47668</v>
       </c>
       <c r="E217">
-        <v>63075</v>
+        <v>63251</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>24601</v>
       </c>
       <c r="C218">
-        <v>33575</v>
+        <v>33579</v>
       </c>
       <c r="D218">
-        <v>55305</v>
+        <v>55334</v>
       </c>
       <c r="E218">
-        <v>70382</v>
+        <v>70446</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>27919</v>
       </c>
       <c r="C219">
-        <v>36131</v>
+        <v>36136</v>
       </c>
       <c r="D219">
-        <v>55618</v>
+        <v>55719</v>
       </c>
       <c r="E219">
-        <v>70341</v>
+        <v>70536</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4094,13 +4094,13 @@
         <v>28286</v>
       </c>
       <c r="C220">
-        <v>37921</v>
+        <v>37940</v>
       </c>
       <c r="D220">
-        <v>58065</v>
+        <v>58297</v>
       </c>
       <c r="E220">
-        <v>72558</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>32643</v>
       </c>
       <c r="C221">
-        <v>43576</v>
+        <v>43580</v>
       </c>
       <c r="D221">
-        <v>64342</v>
+        <v>64387</v>
       </c>
       <c r="E221">
-        <v>77563</v>
+        <v>77622</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>27919</v>
       </c>
       <c r="C222">
-        <v>36131</v>
+        <v>36136</v>
       </c>
       <c r="D222">
-        <v>55618</v>
+        <v>55719</v>
       </c>
       <c r="E222">
-        <v>70341</v>
+        <v>70536</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4148,10 +4148,10 @@
         <v>52860</v>
       </c>
       <c r="D223">
-        <v>73462</v>
+        <v>73470</v>
       </c>
       <c r="E223">
-        <v>84842</v>
+        <v>84858</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4165,7 +4165,7 @@
         <v>34798</v>
       </c>
       <c r="D224">
-        <v>58001</v>
+        <v>58003</v>
       </c>
       <c r="E224">
         <v>74932</v>
@@ -4182,10 +4182,10 @@
         <v>25991</v>
       </c>
       <c r="D225">
-        <v>43162</v>
+        <v>43202</v>
       </c>
       <c r="E225">
-        <v>58931</v>
+        <v>59032</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4199,10 +4199,10 @@
         <v>29322</v>
       </c>
       <c r="D226">
-        <v>50211</v>
+        <v>50228</v>
       </c>
       <c r="E226">
-        <v>66618</v>
+        <v>66654</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>21990</v>
       </c>
       <c r="C227">
-        <v>26174</v>
+        <v>26175</v>
       </c>
       <c r="D227">
-        <v>40137</v>
+        <v>40279</v>
       </c>
       <c r="E227">
-        <v>52990</v>
+        <v>53692</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4233,7 +4233,7 @@
         <v>31228</v>
       </c>
       <c r="D228">
-        <v>55946</v>
+        <v>55949</v>
       </c>
       <c r="E228">
         <v>74598</v>
@@ -4247,13 +4247,13 @@
         <v>28286</v>
       </c>
       <c r="C229">
-        <v>37921</v>
+        <v>37940</v>
       </c>
       <c r="D229">
-        <v>58065</v>
+        <v>58297</v>
       </c>
       <c r="E229">
-        <v>72558</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>29865</v>
       </c>
       <c r="C230">
-        <v>37984</v>
+        <v>37992</v>
       </c>
       <c r="D230">
-        <v>56967</v>
+        <v>57063</v>
       </c>
       <c r="E230">
-        <v>71301</v>
+        <v>71474</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4281,13 +4281,13 @@
         <v>31265</v>
       </c>
       <c r="C231">
-        <v>42848</v>
+        <v>42856</v>
       </c>
       <c r="D231">
-        <v>64048</v>
+        <v>64123</v>
       </c>
       <c r="E231">
-        <v>77391</v>
+        <v>77464</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4301,10 +4301,10 @@
         <v>38176</v>
       </c>
       <c r="D232">
-        <v>59707</v>
+        <v>59742</v>
       </c>
       <c r="E232">
-        <v>73990</v>
+        <v>74059</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4318,10 +4318,10 @@
         <v>47079</v>
       </c>
       <c r="D233">
-        <v>69280</v>
+        <v>69292</v>
       </c>
       <c r="E233">
-        <v>81879</v>
+        <v>81901</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4335,7 +4335,7 @@
         <v>50360</v>
       </c>
       <c r="D234">
-        <v>70168</v>
+        <v>70170</v>
       </c>
       <c r="E234">
         <v>82912</v>
@@ -4352,7 +4352,7 @@
         <v>50360</v>
       </c>
       <c r="D235">
-        <v>70168</v>
+        <v>70170</v>
       </c>
       <c r="E235">
         <v>82912</v>
@@ -4369,10 +4369,10 @@
         <v>51676</v>
       </c>
       <c r="D236">
-        <v>72160</v>
+        <v>72162</v>
       </c>
       <c r="E236">
-        <v>83733</v>
+        <v>83746</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>23365</v>
       </c>
       <c r="C237">
-        <v>30088</v>
+        <v>30089</v>
       </c>
       <c r="D237">
-        <v>50304</v>
+        <v>50326</v>
       </c>
       <c r="E237">
-        <v>66177</v>
+        <v>66212</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>22100</v>
       </c>
       <c r="C238">
-        <v>26900</v>
+        <v>26901</v>
       </c>
       <c r="D238">
-        <v>43647</v>
+        <v>43695</v>
       </c>
       <c r="E238">
-        <v>58783</v>
+        <v>58882</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4420,10 +4420,10 @@
         <v>36316</v>
       </c>
       <c r="D239">
-        <v>59670</v>
+        <v>59672</v>
       </c>
       <c r="E239">
-        <v>75164</v>
+        <v>75175</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4437,7 +4437,7 @@
         <v>33201</v>
       </c>
       <c r="D240">
-        <v>55408</v>
+        <v>55413</v>
       </c>
       <c r="E240">
         <v>71897</v>
@@ -4454,10 +4454,10 @@
         <v>34804</v>
       </c>
       <c r="D241">
-        <v>58475</v>
+        <v>58479</v>
       </c>
       <c r="E241">
-        <v>73872</v>
+        <v>73890</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>32643</v>
       </c>
       <c r="C242">
-        <v>43576</v>
+        <v>43580</v>
       </c>
       <c r="D242">
-        <v>64342</v>
+        <v>64387</v>
       </c>
       <c r="E242">
-        <v>77563</v>
+        <v>77622</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4485,13 +4485,13 @@
         <v>35995</v>
       </c>
       <c r="C243">
-        <v>47432</v>
+        <v>47444</v>
       </c>
       <c r="D243">
-        <v>67089</v>
+        <v>67156</v>
       </c>
       <c r="E243">
-        <v>79424</v>
+        <v>79484</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>32643</v>
       </c>
       <c r="C244">
-        <v>43576</v>
+        <v>43580</v>
       </c>
       <c r="D244">
-        <v>64342</v>
+        <v>64387</v>
       </c>
       <c r="E244">
-        <v>77563</v>
+        <v>77622</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4519,10 +4519,10 @@
         <v>41071</v>
       </c>
       <c r="C245">
-        <v>54869</v>
+        <v>54873</v>
       </c>
       <c r="D245">
-        <v>73580</v>
+        <v>73592</v>
       </c>
       <c r="E245">
         <v>85343</v>
@@ -4536,10 +4536,10 @@
         <v>40152</v>
       </c>
       <c r="C246">
-        <v>54657</v>
+        <v>54661</v>
       </c>
       <c r="D246">
-        <v>73903</v>
+        <v>73916</v>
       </c>
       <c r="E246">
         <v>85730</v>
@@ -4553,10 +4553,10 @@
         <v>40152</v>
       </c>
       <c r="C247">
-        <v>54657</v>
+        <v>54661</v>
       </c>
       <c r="D247">
-        <v>73903</v>
+        <v>73916</v>
       </c>
       <c r="E247">
         <v>85730</v>
@@ -4570,10 +4570,10 @@
         <v>31662</v>
       </c>
       <c r="C248">
-        <v>44647</v>
+        <v>44648</v>
       </c>
       <c r="D248">
-        <v>66644</v>
+        <v>66651</v>
       </c>
       <c r="E248">
         <v>81064</v>
@@ -4587,13 +4587,13 @@
         <v>22890</v>
       </c>
       <c r="C249">
-        <v>32469</v>
+        <v>32470</v>
       </c>
       <c r="D249">
-        <v>57971</v>
+        <v>57974</v>
       </c>
       <c r="E249">
-        <v>75595</v>
+        <v>75609</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>44077</v>
       </c>
       <c r="C250">
-        <v>54541</v>
+        <v>54550</v>
       </c>
       <c r="D250">
-        <v>71491</v>
+        <v>71553</v>
       </c>
       <c r="E250">
-        <v>82446</v>
+        <v>82486</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4621,13 +4621,13 @@
         <v>46957</v>
       </c>
       <c r="C251">
-        <v>57996</v>
+        <v>58035</v>
       </c>
       <c r="D251">
-        <v>74522</v>
+        <v>74605</v>
       </c>
       <c r="E251">
-        <v>84837</v>
+        <v>84879</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4641,10 +4641,10 @@
         <v>52588</v>
       </c>
       <c r="D252">
-        <v>70071</v>
+        <v>70099</v>
       </c>
       <c r="E252">
-        <v>81415</v>
+        <v>81453</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>47973</v>
       </c>
       <c r="C253">
-        <v>60648</v>
+        <v>60652</v>
       </c>
       <c r="D253">
-        <v>78069</v>
+        <v>78080</v>
       </c>
       <c r="E253">
-        <v>88037</v>
+        <v>88045</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>52232</v>
       </c>
       <c r="C254">
-        <v>64206</v>
+        <v>64219</v>
       </c>
       <c r="D254">
-        <v>80454</v>
+        <v>80463</v>
       </c>
       <c r="E254">
-        <v>89779</v>
+        <v>89785</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>47973</v>
       </c>
       <c r="C255">
-        <v>60648</v>
+        <v>60652</v>
       </c>
       <c r="D255">
-        <v>78069</v>
+        <v>78080</v>
       </c>
       <c r="E255">
-        <v>88037</v>
+        <v>88045</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4709,10 +4709,10 @@
         <v>57531</v>
       </c>
       <c r="D256">
-        <v>75672</v>
+        <v>75674</v>
       </c>
       <c r="E256">
-        <v>86127</v>
+        <v>86136</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4723,13 +4723,13 @@
         <v>38229</v>
       </c>
       <c r="C257">
-        <v>51413</v>
+        <v>51414</v>
       </c>
       <c r="D257">
-        <v>71305</v>
+        <v>71315</v>
       </c>
       <c r="E257">
-        <v>82993</v>
+        <v>83005</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4743,10 +4743,10 @@
         <v>50907</v>
       </c>
       <c r="D258">
-        <v>70183</v>
+        <v>70185</v>
       </c>
       <c r="E258">
-        <v>82073</v>
+        <v>82082</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4760,10 +4760,10 @@
         <v>50907</v>
       </c>
       <c r="D259">
-        <v>70183</v>
+        <v>70185</v>
       </c>
       <c r="E259">
-        <v>82073</v>
+        <v>82082</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4777,10 +4777,10 @@
         <v>26512</v>
       </c>
       <c r="D260">
-        <v>49206</v>
+        <v>49257</v>
       </c>
       <c r="E260">
-        <v>65922</v>
+        <v>65988</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>23264</v>
       </c>
       <c r="D261">
-        <v>49135</v>
+        <v>49137</v>
       </c>
       <c r="E261">
-        <v>67105</v>
+        <v>67119</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4811,10 +4811,10 @@
         <v>26149</v>
       </c>
       <c r="D262">
-        <v>48521</v>
+        <v>48568</v>
       </c>
       <c r="E262">
-        <v>65101</v>
+        <v>65166</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4828,7 +4828,7 @@
         <v>32353</v>
       </c>
       <c r="D263">
-        <v>55829</v>
+        <v>55838</v>
       </c>
       <c r="E263">
         <v>72843</v>
@@ -4845,10 +4845,10 @@
         <v>29549</v>
       </c>
       <c r="D264">
-        <v>53754</v>
+        <v>53757</v>
       </c>
       <c r="E264">
-        <v>70403</v>
+        <v>70422</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4862,10 +4862,10 @@
         <v>29549</v>
       </c>
       <c r="D265">
-        <v>53754</v>
+        <v>53757</v>
       </c>
       <c r="E265">
-        <v>70403</v>
+        <v>70422</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>27399</v>
       </c>
       <c r="C266">
-        <v>40419</v>
+        <v>40421</v>
       </c>
       <c r="D266">
-        <v>63310</v>
+        <v>63324</v>
       </c>
       <c r="E266">
-        <v>78404</v>
+        <v>78426</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4896,10 +4896,10 @@
         <v>29549</v>
       </c>
       <c r="D267">
-        <v>53754</v>
+        <v>53757</v>
       </c>
       <c r="E267">
-        <v>70403</v>
+        <v>70422</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4913,10 +4913,10 @@
         <v>23264</v>
       </c>
       <c r="D268">
-        <v>49135</v>
+        <v>49137</v>
       </c>
       <c r="E268">
-        <v>67105</v>
+        <v>67119</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4930,10 +4930,10 @@
         <v>23264</v>
       </c>
       <c r="D269">
-        <v>49135</v>
+        <v>49137</v>
       </c>
       <c r="E269">
-        <v>67105</v>
+        <v>67119</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4947,10 +4947,10 @@
         <v>28699</v>
       </c>
       <c r="D270">
-        <v>54774</v>
+        <v>54781</v>
       </c>
       <c r="E270">
-        <v>71294</v>
+        <v>71313</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4964,10 +4964,10 @@
         <v>20157</v>
       </c>
       <c r="D271">
-        <v>45663</v>
+        <v>45666</v>
       </c>
       <c r="E271">
-        <v>63634</v>
+        <v>63644</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4981,10 +4981,10 @@
         <v>20157</v>
       </c>
       <c r="D272">
-        <v>45663</v>
+        <v>45666</v>
       </c>
       <c r="E272">
-        <v>63634</v>
+        <v>63644</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>17940</v>
       </c>
       <c r="C273">
-        <v>32187</v>
+        <v>32188</v>
       </c>
       <c r="D273">
-        <v>57757</v>
+        <v>57768</v>
       </c>
       <c r="E273">
-        <v>73766</v>
+        <v>73789</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>17940</v>
       </c>
       <c r="C274">
-        <v>32187</v>
+        <v>32188</v>
       </c>
       <c r="D274">
-        <v>57757</v>
+        <v>57768</v>
       </c>
       <c r="E274">
-        <v>73766</v>
+        <v>73789</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5032,10 +5032,10 @@
         <v>16069</v>
       </c>
       <c r="D275">
-        <v>35673</v>
+        <v>35690</v>
       </c>
       <c r="E275">
-        <v>53411</v>
+        <v>53428</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>14723</v>
       </c>
       <c r="D276">
-        <v>36207</v>
+        <v>36208</v>
       </c>
       <c r="E276">
-        <v>55215</v>
+        <v>55219</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5066,10 +5066,10 @@
         <v>26038</v>
       </c>
       <c r="D277">
-        <v>51565</v>
+        <v>51567</v>
       </c>
       <c r="E277">
-        <v>70858</v>
+        <v>70862</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>24657</v>
       </c>
       <c r="C278">
-        <v>36649</v>
+        <v>36650</v>
       </c>
       <c r="D278">
-        <v>63076</v>
+        <v>63078</v>
       </c>
       <c r="E278">
-        <v>79932</v>
+        <v>79936</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>34645</v>
       </c>
       <c r="D279">
-        <v>59718</v>
+        <v>59719</v>
       </c>
       <c r="E279">
-        <v>76890</v>
+        <v>76896</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>34645</v>
       </c>
       <c r="D280">
-        <v>59718</v>
+        <v>59719</v>
       </c>
       <c r="E280">
-        <v>76890</v>
+        <v>76896</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5131,13 +5131,13 @@
         <v>9606</v>
       </c>
       <c r="C281">
-        <v>16625</v>
+        <v>16626</v>
       </c>
       <c r="D281">
-        <v>39954</v>
+        <v>39956</v>
       </c>
       <c r="E281">
-        <v>59947</v>
+        <v>59954</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5151,10 +5151,10 @@
         <v>14455</v>
       </c>
       <c r="D282">
-        <v>36171</v>
+        <v>36172</v>
       </c>
       <c r="E282">
-        <v>55264</v>
+        <v>55270</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5168,10 +5168,10 @@
         <v>14455</v>
       </c>
       <c r="D283">
-        <v>36171</v>
+        <v>36172</v>
       </c>
       <c r="E283">
-        <v>55264</v>
+        <v>55270</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5185,10 +5185,10 @@
         <v>14455</v>
       </c>
       <c r="D284">
-        <v>36171</v>
+        <v>36172</v>
       </c>
       <c r="E284">
-        <v>55264</v>
+        <v>55270</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>14723</v>
       </c>
       <c r="D285">
-        <v>36207</v>
+        <v>36208</v>
       </c>
       <c r="E285">
-        <v>55215</v>
+        <v>55219</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>34645</v>
       </c>
       <c r="D286">
-        <v>59718</v>
+        <v>59719</v>
       </c>
       <c r="E286">
-        <v>76890</v>
+        <v>76896</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5233,10 +5233,10 @@
         <v>38093</v>
       </c>
       <c r="C287">
-        <v>49973</v>
+        <v>49974</v>
       </c>
       <c r="D287">
-        <v>68941</v>
+        <v>68955</v>
       </c>
       <c r="E287">
         <v>82749</v>
@@ -5250,10 +5250,10 @@
         <v>32233</v>
       </c>
       <c r="C288">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="D288">
-        <v>66054</v>
+        <v>66071</v>
       </c>
       <c r="E288">
         <v>80383</v>
@@ -5267,13 +5267,13 @@
         <v>43731</v>
       </c>
       <c r="C289">
-        <v>54755</v>
+        <v>54771</v>
       </c>
       <c r="D289">
-        <v>73282</v>
+        <v>73295</v>
       </c>
       <c r="E289">
-        <v>85331</v>
+        <v>85341</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5284,13 +5284,13 @@
         <v>39535</v>
       </c>
       <c r="C290">
-        <v>51417</v>
+        <v>51418</v>
       </c>
       <c r="D290">
-        <v>70816</v>
+        <v>70831</v>
       </c>
       <c r="E290">
-        <v>83552</v>
+        <v>83563</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,10 +5301,10 @@
         <v>29726</v>
       </c>
       <c r="C291">
-        <v>42915</v>
+        <v>42920</v>
       </c>
       <c r="D291">
-        <v>63955</v>
+        <v>63973</v>
       </c>
       <c r="E291">
         <v>78590</v>
@@ -5321,7 +5321,7 @@
         <v>46636</v>
       </c>
       <c r="D292">
-        <v>66538</v>
+        <v>66552</v>
       </c>
       <c r="E292">
         <v>79942</v>
@@ -5338,7 +5338,7 @@
         <v>46870</v>
       </c>
       <c r="D293">
-        <v>66745</v>
+        <v>66757</v>
       </c>
       <c r="E293">
         <v>80271</v>
@@ -5355,10 +5355,10 @@
         <v>48480</v>
       </c>
       <c r="D294">
-        <v>68595</v>
+        <v>68608</v>
       </c>
       <c r="E294">
-        <v>80843</v>
+        <v>80861</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>23157</v>
       </c>
       <c r="C295">
-        <v>31286</v>
+        <v>31293</v>
       </c>
       <c r="D295">
-        <v>50421</v>
+        <v>50468</v>
       </c>
       <c r="E295">
-        <v>65837</v>
+        <v>65952</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>25852</v>
       </c>
       <c r="C296">
-        <v>34362</v>
+        <v>34365</v>
       </c>
       <c r="D296">
-        <v>53459</v>
+        <v>53506</v>
       </c>
       <c r="E296">
-        <v>68639</v>
+        <v>68751</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>28062</v>
       </c>
       <c r="C297">
-        <v>39500</v>
+        <v>39503</v>
       </c>
       <c r="D297">
-        <v>61459</v>
+        <v>61502</v>
       </c>
       <c r="E297">
-        <v>76166</v>
+        <v>76217</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>22603</v>
       </c>
       <c r="C298">
-        <v>30996</v>
+        <v>31000</v>
       </c>
       <c r="D298">
-        <v>50669</v>
+        <v>50711</v>
       </c>
       <c r="E298">
-        <v>66342</v>
+        <v>66455</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>24380</v>
       </c>
       <c r="C299">
-        <v>35407</v>
+        <v>35409</v>
       </c>
       <c r="D299">
-        <v>57804</v>
+        <v>57828</v>
       </c>
       <c r="E299">
-        <v>73150</v>
+        <v>73198</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>23157</v>
       </c>
       <c r="C300">
-        <v>31286</v>
+        <v>31293</v>
       </c>
       <c r="D300">
-        <v>50421</v>
+        <v>50468</v>
       </c>
       <c r="E300">
-        <v>65837</v>
+        <v>65952</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>28505</v>
       </c>
       <c r="C301">
-        <v>39147</v>
+        <v>39149</v>
       </c>
       <c r="D301">
-        <v>60402</v>
+        <v>60424</v>
       </c>
       <c r="E301">
-        <v>75130</v>
+        <v>75172</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5491,7 +5491,7 @@
         <v>42567</v>
       </c>
       <c r="D302">
-        <v>65015</v>
+        <v>65019</v>
       </c>
       <c r="E302">
         <v>80366</v>
@@ -5508,10 +5508,10 @@
         <v>44021</v>
       </c>
       <c r="D303">
-        <v>67033</v>
+        <v>67037</v>
       </c>
       <c r="E303">
-        <v>81255</v>
+        <v>81266</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>22903</v>
       </c>
       <c r="C304">
-        <v>32761</v>
+        <v>32762</v>
       </c>
       <c r="D304">
-        <v>54496</v>
+        <v>54524</v>
       </c>
       <c r="E304">
-        <v>70001</v>
+        <v>70049</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>22903</v>
       </c>
       <c r="C305">
-        <v>32761</v>
+        <v>32762</v>
       </c>
       <c r="D305">
-        <v>54496</v>
+        <v>54524</v>
       </c>
       <c r="E305">
-        <v>70001</v>
+        <v>70049</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>23225</v>
       </c>
       <c r="C306">
-        <v>31318</v>
+        <v>31320</v>
       </c>
       <c r="D306">
-        <v>51432</v>
+        <v>51440</v>
       </c>
       <c r="E306">
-        <v>66811</v>
+        <v>66839</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>22903</v>
       </c>
       <c r="C307">
-        <v>32761</v>
+        <v>32762</v>
       </c>
       <c r="D307">
-        <v>54496</v>
+        <v>54524</v>
       </c>
       <c r="E307">
-        <v>70001</v>
+        <v>70049</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5593,7 +5593,7 @@
         <v>36829</v>
       </c>
       <c r="D308">
-        <v>58750</v>
+        <v>58751</v>
       </c>
       <c r="E308">
         <v>74934</v>
@@ -5607,13 +5607,13 @@
         <v>23225</v>
       </c>
       <c r="C309">
-        <v>31318</v>
+        <v>31320</v>
       </c>
       <c r="D309">
-        <v>51432</v>
+        <v>51440</v>
       </c>
       <c r="E309">
-        <v>66811</v>
+        <v>66839</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5627,7 +5627,7 @@
         <v>39462</v>
       </c>
       <c r="D310">
-        <v>62383</v>
+        <v>62388</v>
       </c>
       <c r="E310">
         <v>77951</v>
@@ -5644,10 +5644,10 @@
         <v>19633</v>
       </c>
       <c r="D311">
-        <v>44028</v>
+        <v>44029</v>
       </c>
       <c r="E311">
-        <v>62812</v>
+        <v>62818</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5661,10 +5661,10 @@
         <v>16379</v>
       </c>
       <c r="D312">
-        <v>33425</v>
+        <v>33426</v>
       </c>
       <c r="E312">
-        <v>47108</v>
+        <v>47177</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5678,10 +5678,10 @@
         <v>19633</v>
       </c>
       <c r="D313">
-        <v>44028</v>
+        <v>44029</v>
       </c>
       <c r="E313">
-        <v>62812</v>
+        <v>62818</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5695,10 +5695,10 @@
         <v>19633</v>
       </c>
       <c r="D314">
-        <v>44028</v>
+        <v>44029</v>
       </c>
       <c r="E314">
-        <v>62812</v>
+        <v>62818</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>40094</v>
       </c>
       <c r="C315">
-        <v>50580</v>
+        <v>50607</v>
       </c>
       <c r="D315">
-        <v>68546</v>
+        <v>68614</v>
       </c>
       <c r="E315">
-        <v>80563</v>
+        <v>80604</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5723,16 +5723,16 @@
         <v>315</v>
       </c>
       <c r="B316">
-        <v>43566</v>
+        <v>43569</v>
       </c>
       <c r="C316">
-        <v>52516</v>
+        <v>52568</v>
       </c>
       <c r="D316">
-        <v>68233</v>
+        <v>68335</v>
       </c>
       <c r="E316">
-        <v>80066</v>
+        <v>80163</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>43061</v>
       </c>
       <c r="C317">
-        <v>51498</v>
+        <v>51536</v>
       </c>
       <c r="D317">
-        <v>67119</v>
+        <v>67258</v>
       </c>
       <c r="E317">
-        <v>79012</v>
+        <v>79120</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>40703</v>
       </c>
       <c r="C318">
-        <v>49509</v>
+        <v>49539</v>
       </c>
       <c r="D318">
-        <v>65768</v>
+        <v>65899</v>
       </c>
       <c r="E318">
-        <v>78171</v>
+        <v>78280</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>36384</v>
       </c>
       <c r="C319">
-        <v>45034</v>
+        <v>45054</v>
       </c>
       <c r="D319">
-        <v>61699</v>
+        <v>61847</v>
       </c>
       <c r="E319">
-        <v>74430</v>
+        <v>74553</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>38381</v>
       </c>
       <c r="C320">
-        <v>47209</v>
+        <v>47262</v>
       </c>
       <c r="D320">
-        <v>63575</v>
+        <v>63750</v>
       </c>
       <c r="E320">
-        <v>76149</v>
+        <v>76276</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>40694</v>
       </c>
       <c r="C321">
-        <v>49349</v>
+        <v>49396</v>
       </c>
       <c r="D321">
-        <v>65420</v>
+        <v>65570</v>
       </c>
       <c r="E321">
-        <v>77743</v>
+        <v>77853</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>43802</v>
       </c>
       <c r="C322">
-        <v>56059</v>
+        <v>56062</v>
       </c>
       <c r="D322">
-        <v>74390</v>
+        <v>74401</v>
       </c>
       <c r="E322">
-        <v>85587</v>
+        <v>85596</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>39481</v>
       </c>
       <c r="C323">
-        <v>47673</v>
+        <v>47683</v>
       </c>
       <c r="D323">
-        <v>63283</v>
+        <v>63408</v>
       </c>
       <c r="E323">
-        <v>75634</v>
+        <v>75743</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>39481</v>
       </c>
       <c r="C324">
-        <v>47673</v>
+        <v>47683</v>
       </c>
       <c r="D324">
-        <v>63283</v>
+        <v>63408</v>
       </c>
       <c r="E324">
-        <v>75634</v>
+        <v>75743</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>39481</v>
       </c>
       <c r="C325">
-        <v>47673</v>
+        <v>47683</v>
       </c>
       <c r="D325">
-        <v>63283</v>
+        <v>63408</v>
       </c>
       <c r="E325">
-        <v>75634</v>
+        <v>75743</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>42703</v>
       </c>
       <c r="C326">
-        <v>51135</v>
+        <v>51157</v>
       </c>
       <c r="D326">
-        <v>66606</v>
+        <v>66737</v>
       </c>
       <c r="E326">
-        <v>78580</v>
+        <v>78691</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,10 +5913,10 @@
         <v>40094</v>
       </c>
       <c r="C327">
-        <v>52388</v>
+        <v>52393</v>
       </c>
       <c r="D327">
-        <v>70749</v>
+        <v>70764</v>
       </c>
       <c r="E327">
         <v>83215</v>
@@ -5930,13 +5930,13 @@
         <v>41904</v>
       </c>
       <c r="C328">
-        <v>54145</v>
+        <v>54149</v>
       </c>
       <c r="D328">
-        <v>72747</v>
+        <v>72762</v>
       </c>
       <c r="E328">
-        <v>84067</v>
+        <v>84076</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>38913</v>
       </c>
       <c r="C329">
-        <v>51639</v>
+        <v>51641</v>
       </c>
       <c r="D329">
-        <v>71189</v>
+        <v>71203</v>
       </c>
       <c r="E329">
-        <v>83077</v>
+        <v>83088</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>41904</v>
       </c>
       <c r="C330">
-        <v>54145</v>
+        <v>54149</v>
       </c>
       <c r="D330">
-        <v>72747</v>
+        <v>72762</v>
       </c>
       <c r="E330">
-        <v>84067</v>
+        <v>84076</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>36252</v>
       </c>
       <c r="C331">
-        <v>46380</v>
+        <v>46391</v>
       </c>
       <c r="D331">
-        <v>64844</v>
+        <v>64930</v>
       </c>
       <c r="E331">
-        <v>77324</v>
+        <v>77371</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,10 +5998,10 @@
         <v>42308</v>
       </c>
       <c r="C332">
-        <v>55196</v>
+        <v>55201</v>
       </c>
       <c r="D332">
-        <v>74067</v>
+        <v>74079</v>
       </c>
       <c r="E332">
         <v>86135</v>
@@ -6015,13 +6015,13 @@
         <v>40020</v>
       </c>
       <c r="C333">
-        <v>51585</v>
+        <v>51599</v>
       </c>
       <c r="D333">
-        <v>71188</v>
+        <v>71248</v>
       </c>
       <c r="E333">
-        <v>83302</v>
+        <v>83348</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,10 +6032,10 @@
         <v>46547</v>
       </c>
       <c r="C334">
-        <v>60402</v>
+        <v>60411</v>
       </c>
       <c r="D334">
-        <v>78654</v>
+        <v>78664</v>
       </c>
       <c r="E334">
         <v>89479</v>
@@ -6049,10 +6049,10 @@
         <v>44118</v>
       </c>
       <c r="C335">
-        <v>58151</v>
+        <v>58157</v>
       </c>
       <c r="D335">
-        <v>77246</v>
+        <v>77257</v>
       </c>
       <c r="E335">
         <v>88618</v>
@@ -6069,10 +6069,10 @@
         <v>54299</v>
       </c>
       <c r="D336">
-        <v>73783</v>
+        <v>73797</v>
       </c>
       <c r="E336">
-        <v>85201</v>
+        <v>85210</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6086,10 +6086,10 @@
         <v>17254</v>
       </c>
       <c r="D337">
-        <v>33254</v>
+        <v>33267</v>
       </c>
       <c r="E337">
-        <v>47710</v>
+        <v>47721</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6103,10 +6103,10 @@
         <v>16758</v>
       </c>
       <c r="D338">
-        <v>32582</v>
+        <v>32586</v>
       </c>
       <c r="E338">
-        <v>46799</v>
+        <v>46806</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6120,10 +6120,10 @@
         <v>17254</v>
       </c>
       <c r="D339">
-        <v>33254</v>
+        <v>33267</v>
       </c>
       <c r="E339">
-        <v>47710</v>
+        <v>47721</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>17750</v>
       </c>
       <c r="D340">
-        <v>35698</v>
+        <v>35699</v>
       </c>
       <c r="E340">
-        <v>51833</v>
+        <v>51835</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,7 +6154,7 @@
         <v>17262</v>
       </c>
       <c r="D341">
-        <v>34679</v>
+        <v>34680</v>
       </c>
       <c r="E341">
         <v>51105</v>
@@ -6171,10 +6171,10 @@
         <v>20799</v>
       </c>
       <c r="D342">
-        <v>40734</v>
+        <v>40735</v>
       </c>
       <c r="E342">
-        <v>57915</v>
+        <v>57918</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6188,10 +6188,10 @@
         <v>20799</v>
       </c>
       <c r="D343">
-        <v>40734</v>
+        <v>40735</v>
       </c>
       <c r="E343">
-        <v>57915</v>
+        <v>57918</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>17750</v>
       </c>
       <c r="D344">
-        <v>35698</v>
+        <v>35699</v>
       </c>
       <c r="E344">
-        <v>51833</v>
+        <v>51835</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6225,7 +6225,7 @@
         <v>30598</v>
       </c>
       <c r="E345">
-        <v>45605</v>
+        <v>45607</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6242,7 +6242,7 @@
         <v>30598</v>
       </c>
       <c r="E346">
-        <v>45605</v>
+        <v>45607</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6259,7 +6259,7 @@
         <v>30598</v>
       </c>
       <c r="E347">
-        <v>45605</v>
+        <v>45607</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6273,10 +6273,10 @@
         <v>20201</v>
       </c>
       <c r="D348">
-        <v>37830</v>
+        <v>37832</v>
       </c>
       <c r="E348">
-        <v>53919</v>
+        <v>53922</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6290,10 +6290,10 @@
         <v>20201</v>
       </c>
       <c r="D349">
-        <v>37830</v>
+        <v>37832</v>
       </c>
       <c r="E349">
-        <v>53919</v>
+        <v>53922</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6307,10 +6307,10 @@
         <v>20201</v>
       </c>
       <c r="D350">
-        <v>37830</v>
+        <v>37832</v>
       </c>
       <c r="E350">
-        <v>53919</v>
+        <v>53922</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6327,7 +6327,7 @@
         <v>27930</v>
       </c>
       <c r="E351">
-        <v>41188</v>
+        <v>41191</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6344,7 +6344,7 @@
         <v>27930</v>
       </c>
       <c r="E352">
-        <v>41188</v>
+        <v>41191</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6358,7 +6358,7 @@
         <v>26222</v>
       </c>
       <c r="D353">
-        <v>47508</v>
+        <v>47512</v>
       </c>
       <c r="E353">
         <v>65904</v>
@@ -6378,7 +6378,7 @@
         <v>41197</v>
       </c>
       <c r="E354">
-        <v>58309</v>
+        <v>58314</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6392,10 +6392,10 @@
         <v>27162</v>
       </c>
       <c r="D355">
-        <v>49206</v>
+        <v>49209</v>
       </c>
       <c r="E355">
-        <v>66888</v>
+        <v>66898</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6409,10 +6409,10 @@
         <v>19782</v>
       </c>
       <c r="D356">
-        <v>37042</v>
+        <v>37043</v>
       </c>
       <c r="E356">
-        <v>53633</v>
+        <v>53635</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6426,10 +6426,10 @@
         <v>19782</v>
       </c>
       <c r="D357">
-        <v>37042</v>
+        <v>37043</v>
       </c>
       <c r="E357">
-        <v>53633</v>
+        <v>53635</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6443,10 +6443,10 @@
         <v>19782</v>
       </c>
       <c r="D358">
-        <v>37042</v>
+        <v>37043</v>
       </c>
       <c r="E358">
-        <v>53633</v>
+        <v>53635</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6460,10 +6460,10 @@
         <v>12540</v>
       </c>
       <c r="D359">
-        <v>28740</v>
+        <v>28741</v>
       </c>
       <c r="E359">
-        <v>42781</v>
+        <v>42782</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6477,10 +6477,10 @@
         <v>12540</v>
       </c>
       <c r="D360">
-        <v>28740</v>
+        <v>28741</v>
       </c>
       <c r="E360">
-        <v>42781</v>
+        <v>42782</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6494,7 +6494,7 @@
         <v>41024</v>
       </c>
       <c r="D361">
-        <v>66230</v>
+        <v>66235</v>
       </c>
       <c r="E361">
         <v>81942</v>
@@ -6511,10 +6511,10 @@
         <v>39464</v>
       </c>
       <c r="D362">
-        <v>66451</v>
+        <v>66463</v>
       </c>
       <c r="E362">
-        <v>81555</v>
+        <v>81576</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>35047</v>
       </c>
       <c r="D363">
-        <v>62303</v>
+        <v>62305</v>
       </c>
       <c r="E363">
-        <v>78938</v>
+        <v>78949</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6545,10 +6545,10 @@
         <v>41212</v>
       </c>
       <c r="D364">
-        <v>66721</v>
+        <v>66722</v>
       </c>
       <c r="E364">
-        <v>81868</v>
+        <v>81876</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6562,10 +6562,10 @@
         <v>41212</v>
       </c>
       <c r="D365">
-        <v>66721</v>
+        <v>66722</v>
       </c>
       <c r="E365">
-        <v>81868</v>
+        <v>81876</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6579,10 +6579,10 @@
         <v>33858</v>
       </c>
       <c r="D366">
-        <v>60848</v>
+        <v>60851</v>
       </c>
       <c r="E366">
-        <v>77622</v>
+        <v>77641</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6596,10 +6596,10 @@
         <v>33858</v>
       </c>
       <c r="D367">
-        <v>60848</v>
+        <v>60851</v>
       </c>
       <c r="E367">
-        <v>77622</v>
+        <v>77641</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6613,10 +6613,10 @@
         <v>35490</v>
       </c>
       <c r="D368">
-        <v>61809</v>
+        <v>61810</v>
       </c>
       <c r="E368">
-        <v>78356</v>
+        <v>78365</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6630,10 +6630,10 @@
         <v>33858</v>
       </c>
       <c r="D369">
-        <v>60848</v>
+        <v>60851</v>
       </c>
       <c r="E369">
-        <v>77622</v>
+        <v>77641</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6647,10 +6647,10 @@
         <v>27264</v>
       </c>
       <c r="D370">
-        <v>55583</v>
+        <v>55590</v>
       </c>
       <c r="E370">
-        <v>73900</v>
+        <v>73921</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6664,10 +6664,10 @@
         <v>27264</v>
       </c>
       <c r="D371">
-        <v>55583</v>
+        <v>55590</v>
       </c>
       <c r="E371">
-        <v>73900</v>
+        <v>73921</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6681,10 +6681,10 @@
         <v>27264</v>
       </c>
       <c r="D372">
-        <v>55583</v>
+        <v>55590</v>
       </c>
       <c r="E372">
-        <v>73900</v>
+        <v>73921</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6698,7 +6698,7 @@
         <v>33228</v>
       </c>
       <c r="D373">
-        <v>55809</v>
+        <v>55811</v>
       </c>
       <c r="E373">
         <v>71824</v>
@@ -6715,7 +6715,7 @@
         <v>25186</v>
       </c>
       <c r="D374">
-        <v>46931</v>
+        <v>46933</v>
       </c>
       <c r="E374">
         <v>65191</v>
@@ -6732,10 +6732,10 @@
         <v>34147</v>
       </c>
       <c r="D375">
-        <v>57594</v>
+        <v>57596</v>
       </c>
       <c r="E375">
-        <v>72714</v>
+        <v>72716</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>18733</v>
       </c>
       <c r="C376">
-        <v>26415</v>
+        <v>26416</v>
       </c>
       <c r="D376">
-        <v>49587</v>
+        <v>49590</v>
       </c>
       <c r="E376">
-        <v>67142</v>
+        <v>67144</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>18733</v>
       </c>
       <c r="C377">
-        <v>26415</v>
+        <v>26416</v>
       </c>
       <c r="D377">
-        <v>49587</v>
+        <v>49590</v>
       </c>
       <c r="E377">
-        <v>67142</v>
+        <v>67144</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6783,7 +6783,7 @@
         <v>38991</v>
       </c>
       <c r="D378">
-        <v>61127</v>
+        <v>61128</v>
       </c>
       <c r="E378">
         <v>76240</v>
@@ -6800,7 +6800,7 @@
         <v>38991</v>
       </c>
       <c r="D379">
-        <v>61127</v>
+        <v>61128</v>
       </c>
       <c r="E379">
         <v>76240</v>
@@ -6817,10 +6817,10 @@
         <v>39927</v>
       </c>
       <c r="D380">
-        <v>63047</v>
+        <v>63048</v>
       </c>
       <c r="E380">
-        <v>77128</v>
+        <v>77136</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6834,10 +6834,10 @@
         <v>39927</v>
       </c>
       <c r="D381">
-        <v>63047</v>
+        <v>63048</v>
       </c>
       <c r="E381">
-        <v>77128</v>
+        <v>77136</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>23438</v>
       </c>
       <c r="C382">
-        <v>34036</v>
+        <v>34037</v>
       </c>
       <c r="D382">
-        <v>58189</v>
+        <v>58191</v>
       </c>
       <c r="E382">
-        <v>73865</v>
+        <v>73882</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6868,10 +6868,10 @@
         <v>43057</v>
       </c>
       <c r="D383">
-        <v>65719</v>
+        <v>65722</v>
       </c>
       <c r="E383">
-        <v>79023</v>
+        <v>79040</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6885,10 +6885,10 @@
         <v>35983</v>
       </c>
       <c r="D384">
-        <v>60087</v>
+        <v>60088</v>
       </c>
       <c r="E384">
-        <v>75074</v>
+        <v>75078</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6902,10 +6902,10 @@
         <v>50837</v>
       </c>
       <c r="D385">
-        <v>71367</v>
+        <v>71370</v>
       </c>
       <c r="E385">
-        <v>83136</v>
+        <v>83147</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6919,10 +6919,10 @@
         <v>30252</v>
       </c>
       <c r="D386">
-        <v>54978</v>
+        <v>54979</v>
       </c>
       <c r="E386">
-        <v>71660</v>
+        <v>71668</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6936,10 +6936,10 @@
         <v>30252</v>
       </c>
       <c r="D387">
-        <v>54978</v>
+        <v>54979</v>
       </c>
       <c r="E387">
-        <v>71660</v>
+        <v>71668</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6973,7 +6973,7 @@
         <v>30580</v>
       </c>
       <c r="E389">
-        <v>51010</v>
+        <v>51011</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6990,7 +6990,7 @@
         <v>30580</v>
       </c>
       <c r="E390">
-        <v>51010</v>
+        <v>51011</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7024,7 +7024,7 @@
         <v>30580</v>
       </c>
       <c r="E392">
-        <v>51010</v>
+        <v>51011</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7041,7 +7041,7 @@
         <v>22874</v>
       </c>
       <c r="E393">
-        <v>38110</v>
+        <v>38111</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7058,7 +7058,7 @@
         <v>22874</v>
       </c>
       <c r="E394">
-        <v>38110</v>
+        <v>38111</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7075,7 +7075,7 @@
         <v>23658</v>
       </c>
       <c r="E395">
-        <v>38853</v>
+        <v>38854</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7092,7 +7092,7 @@
         <v>23658</v>
       </c>
       <c r="E396">
-        <v>38853</v>
+        <v>38854</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7160,7 +7160,7 @@
         <v>33329</v>
       </c>
       <c r="E400">
-        <v>55728</v>
+        <v>55734</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7177,7 +7177,7 @@
         <v>33806</v>
       </c>
       <c r="E401">
-        <v>55904</v>
+        <v>55909</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7194,7 +7194,7 @@
         <v>30372</v>
       </c>
       <c r="E402">
-        <v>51770</v>
+        <v>51774</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7211,7 +7211,7 @@
         <v>33329</v>
       </c>
       <c r="E403">
-        <v>55728</v>
+        <v>55734</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7228,7 +7228,7 @@
         <v>29287</v>
       </c>
       <c r="E404">
-        <v>50829</v>
+        <v>50833</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7245,7 +7245,7 @@
         <v>29287</v>
       </c>
       <c r="E405">
-        <v>50829</v>
+        <v>50833</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7262,7 +7262,7 @@
         <v>29287</v>
       </c>
       <c r="E406">
-        <v>50829</v>
+        <v>50833</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7279,7 +7279,7 @@
         <v>26570</v>
       </c>
       <c r="E407">
-        <v>47378</v>
+        <v>47380</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7296,7 +7296,7 @@
         <v>26570</v>
       </c>
       <c r="E408">
-        <v>47378</v>
+        <v>47380</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7313,7 +7313,7 @@
         <v>26570</v>
       </c>
       <c r="E409">
-        <v>47378</v>
+        <v>47380</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7327,7 +7327,7 @@
         <v>25578</v>
       </c>
       <c r="D410">
-        <v>53721</v>
+        <v>53724</v>
       </c>
       <c r="E410">
         <v>73902</v>
@@ -7344,10 +7344,10 @@
         <v>20888</v>
       </c>
       <c r="D411">
-        <v>49831</v>
+        <v>49833</v>
       </c>
       <c r="E411">
-        <v>70670</v>
+        <v>70685</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7361,10 +7361,10 @@
         <v>20888</v>
       </c>
       <c r="D412">
-        <v>49831</v>
+        <v>49833</v>
       </c>
       <c r="E412">
-        <v>70670</v>
+        <v>70685</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7378,10 +7378,10 @@
         <v>19831</v>
       </c>
       <c r="D413">
-        <v>48182</v>
+        <v>48187</v>
       </c>
       <c r="E413">
-        <v>68563</v>
+        <v>68579</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7395,10 +7395,10 @@
         <v>26887</v>
       </c>
       <c r="D414">
-        <v>55781</v>
+        <v>55785</v>
       </c>
       <c r="E414">
-        <v>74903</v>
+        <v>74923</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7412,10 +7412,10 @@
         <v>22380</v>
       </c>
       <c r="D415">
-        <v>51107</v>
+        <v>51108</v>
       </c>
       <c r="E415">
-        <v>71555</v>
+        <v>71564</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>22380</v>
       </c>
       <c r="D416">
-        <v>51107</v>
+        <v>51108</v>
       </c>
       <c r="E416">
-        <v>71555</v>
+        <v>71564</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7449,7 +7449,7 @@
         <v>41756</v>
       </c>
       <c r="E417">
-        <v>63311</v>
+        <v>63322</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7466,7 +7466,7 @@
         <v>41756</v>
       </c>
       <c r="E418">
-        <v>63311</v>
+        <v>63322</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7514,10 +7514,10 @@
         <v>16367</v>
       </c>
       <c r="D421">
-        <v>36824</v>
+        <v>36828</v>
       </c>
       <c r="E421">
-        <v>54749</v>
+        <v>54766</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>16367</v>
       </c>
       <c r="D422">
-        <v>36824</v>
+        <v>36828</v>
       </c>
       <c r="E422">
-        <v>54749</v>
+        <v>54766</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7582,10 +7582,10 @@
         <v>16367</v>
       </c>
       <c r="D425">
-        <v>36824</v>
+        <v>36828</v>
       </c>
       <c r="E425">
-        <v>54749</v>
+        <v>54766</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7619,7 +7619,7 @@
         <v>45775</v>
       </c>
       <c r="E427">
-        <v>64757</v>
+        <v>64761</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7636,7 +7636,7 @@
         <v>45775</v>
       </c>
       <c r="E428">
-        <v>64757</v>
+        <v>64761</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7684,10 +7684,10 @@
         <v>16367</v>
       </c>
       <c r="D431">
-        <v>36824</v>
+        <v>36828</v>
       </c>
       <c r="E431">
-        <v>54749</v>
+        <v>54766</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7772,7 +7772,7 @@
         <v>37187</v>
       </c>
       <c r="E436">
-        <v>56105</v>
+        <v>56110</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7874,7 +7874,7 @@
         <v>27361</v>
       </c>
       <c r="E442">
-        <v>43104</v>
+        <v>43106</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>29319</v>
       </c>
       <c r="D448">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E448">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>29319</v>
       </c>
       <c r="D449">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E449">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>29319</v>
       </c>
       <c r="D450">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E450">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>29319</v>
       </c>
       <c r="D451">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E451">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>29319</v>
       </c>
       <c r="D452">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E452">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>29319</v>
       </c>
       <c r="D453">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E453">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8078,7 +8078,7 @@
         <v>49325</v>
       </c>
       <c r="E454">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8095,7 +8095,7 @@
         <v>49325</v>
       </c>
       <c r="E455">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8112,7 +8112,7 @@
         <v>49325</v>
       </c>
       <c r="E456">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8129,7 +8129,7 @@
         <v>49325</v>
       </c>
       <c r="E457">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8146,7 +8146,7 @@
         <v>49325</v>
       </c>
       <c r="E458">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8163,7 +8163,7 @@
         <v>49325</v>
       </c>
       <c r="E459">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8180,7 +8180,7 @@
         <v>49325</v>
       </c>
       <c r="E460">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8197,7 +8197,7 @@
         <v>49325</v>
       </c>
       <c r="E461">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8214,7 +8214,7 @@
         <v>49325</v>
       </c>
       <c r="E462">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8231,7 +8231,7 @@
         <v>45775</v>
       </c>
       <c r="E463">
-        <v>64757</v>
+        <v>64761</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8248,7 +8248,7 @@
         <v>45775</v>
       </c>
       <c r="E464">
-        <v>64757</v>
+        <v>64761</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8282,7 +8282,7 @@
         <v>36561</v>
       </c>
       <c r="E466">
-        <v>55270</v>
+        <v>55272</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8299,7 +8299,7 @@
         <v>45775</v>
       </c>
       <c r="E467">
-        <v>64757</v>
+        <v>64761</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>29319</v>
       </c>
       <c r="D468">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E468">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>29319</v>
       </c>
       <c r="D469">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E469">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>29319</v>
       </c>
       <c r="D470">
-        <v>53488</v>
+        <v>53489</v>
       </c>
       <c r="E470">
-        <v>70741</v>
+        <v>70743</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8367,7 +8367,7 @@
         <v>45775</v>
       </c>
       <c r="E471">
-        <v>64757</v>
+        <v>64761</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8384,7 +8384,7 @@
         <v>49325</v>
       </c>
       <c r="E472">
-        <v>67961</v>
+        <v>67963</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8401,7 +8401,7 @@
         <v>36561</v>
       </c>
       <c r="E473">
-        <v>55270</v>
+        <v>55272</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8418,7 +8418,7 @@
         <v>36561</v>
       </c>
       <c r="E474">
-        <v>55270</v>
+        <v>55272</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8435,7 +8435,7 @@
         <v>37187</v>
       </c>
       <c r="E475">
-        <v>56105</v>
+        <v>56110</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8452,7 +8452,7 @@
         <v>36204</v>
       </c>
       <c r="E476">
-        <v>55114</v>
+        <v>55118</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8469,7 +8469,7 @@
         <v>36204</v>
       </c>
       <c r="E477">
-        <v>55114</v>
+        <v>55118</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8483,10 +8483,10 @@
         <v>13391</v>
       </c>
       <c r="D478">
-        <v>33448</v>
+        <v>33454</v>
       </c>
       <c r="E478">
-        <v>51860</v>
+        <v>51876</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8500,10 +8500,10 @@
         <v>14923</v>
       </c>
       <c r="D479">
-        <v>38033</v>
+        <v>38034</v>
       </c>
       <c r="E479">
-        <v>57986</v>
+        <v>57988</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8534,10 +8534,10 @@
         <v>13391</v>
       </c>
       <c r="D481">
-        <v>33448</v>
+        <v>33454</v>
       </c>
       <c r="E481">
-        <v>51860</v>
+        <v>51876</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8551,10 +8551,10 @@
         <v>13391</v>
       </c>
       <c r="D482">
-        <v>33448</v>
+        <v>33454</v>
       </c>
       <c r="E482">
-        <v>51860</v>
+        <v>51876</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8568,10 +8568,10 @@
         <v>13391</v>
       </c>
       <c r="D483">
-        <v>33448</v>
+        <v>33454</v>
       </c>
       <c r="E483">
-        <v>51860</v>
+        <v>51876</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8585,10 +8585,10 @@
         <v>13391</v>
       </c>
       <c r="D484">
-        <v>33448</v>
+        <v>33454</v>
       </c>
       <c r="E484">
-        <v>51860</v>
+        <v>51876</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8639,7 +8639,7 @@
         <v>36723</v>
       </c>
       <c r="E487">
-        <v>56237</v>
+        <v>56239</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8653,10 +8653,10 @@
         <v>14989</v>
       </c>
       <c r="D488">
-        <v>37109</v>
+        <v>37110</v>
       </c>
       <c r="E488">
-        <v>56327</v>
+        <v>56330</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8670,10 +8670,10 @@
         <v>14989</v>
       </c>
       <c r="D489">
-        <v>37109</v>
+        <v>37110</v>
       </c>
       <c r="E489">
-        <v>56327</v>
+        <v>56330</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8687,7 +8687,7 @@
         <v>24664</v>
       </c>
       <c r="D490">
-        <v>50985</v>
+        <v>50986</v>
       </c>
       <c r="E490">
         <v>70408</v>
@@ -8704,10 +8704,10 @@
         <v>25765</v>
       </c>
       <c r="D491">
-        <v>52854</v>
+        <v>52855</v>
       </c>
       <c r="E491">
-        <v>71335</v>
+        <v>71344</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8721,7 +8721,7 @@
         <v>24664</v>
       </c>
       <c r="D492">
-        <v>50985</v>
+        <v>50986</v>
       </c>
       <c r="E492">
         <v>70408</v>
@@ -8738,7 +8738,7 @@
         <v>24664</v>
       </c>
       <c r="D493">
-        <v>50985</v>
+        <v>50986</v>
       </c>
       <c r="E493">
         <v>70408</v>
@@ -8755,7 +8755,7 @@
         <v>24664</v>
       </c>
       <c r="D494">
-        <v>50985</v>
+        <v>50986</v>
       </c>
       <c r="E494">
         <v>70408</v>
@@ -8772,10 +8772,10 @@
         <v>26945</v>
       </c>
       <c r="D495">
-        <v>54784</v>
+        <v>54791</v>
       </c>
       <c r="E495">
-        <v>72941</v>
+        <v>72959</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8789,10 +8789,10 @@
         <v>29928</v>
       </c>
       <c r="D496">
-        <v>57284</v>
+        <v>57289</v>
       </c>
       <c r="E496">
-        <v>74677</v>
+        <v>74696</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8806,10 +8806,10 @@
         <v>26945</v>
       </c>
       <c r="D497">
-        <v>54784</v>
+        <v>54791</v>
       </c>
       <c r="E497">
-        <v>72941</v>
+        <v>72959</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8823,10 +8823,10 @@
         <v>27678</v>
       </c>
       <c r="D498">
-        <v>52646</v>
+        <v>52650</v>
       </c>
       <c r="E498">
-        <v>69795</v>
+        <v>69811</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8840,10 +8840,10 @@
         <v>27678</v>
       </c>
       <c r="D499">
-        <v>52646</v>
+        <v>52650</v>
       </c>
       <c r="E499">
-        <v>69795</v>
+        <v>69811</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8857,10 +8857,10 @@
         <v>27678</v>
       </c>
       <c r="D500">
-        <v>52646</v>
+        <v>52650</v>
       </c>
       <c r="E500">
-        <v>69795</v>
+        <v>69811</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8877,7 +8877,7 @@
         <v>38530</v>
       </c>
       <c r="E501">
-        <v>57875</v>
+        <v>57879</v>
       </c>
     </row>
   </sheetData>
